--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4119,8 +4119,53 @@
       <c r="H83" s="5" t="inlineStr"/>
       <c r="I83" s="5" t="inlineStr"/>
     </row>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>CI-83</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Summariser resilience</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Tamil citizen_name → background summarisation completes (SDK ASCII bug)</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit an appointment where citizen name field contains Tamil (e.g. 'ராம் குமார்')
+2. Wait 10s for the background summariser (spawn_bg → _trigger_summarisation)
+3. Tail Railway logs OR open the appointment's GrievanceSummaryRecord in the portal</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Log shows 'Summarisation complete in Nms | model=gemini-2.5-flash | ...' — NOT '[GEMINI WARN] appointment_id=X: ... ascii codec can't encode characters'. GrievanceSummaryRecord row exists.</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Regression for prod appointment 426. Fixed via _sanitize_user_field ascii-strip; UnicodeEncodeError short-circuit in _call_with_fallback.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I83"/>
+  <autoFilter ref="A1:I84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Log shows 'Summarisation complete in Nms | model=gemini-2.5-flash | ...' — NOT '[GEMINI WARN] appointment_id=X: ... ascii codec can't encode characters'. GrievanceSummaryRecord row exists.</t>
+          <t>Log shows 'Summarisation complete in Nms | backend=vertex | ...' — NOT '[GEMINI WARN] appointment_id=X: ... ascii codec can't encode characters'. GrievanceSummaryRecord row exists.</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -4160,12 +4160,58 @@
       <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Regression for prod appointment 426. Fixed via _sanitize_user_field ascii-strip; UnicodeEncodeError short-circuit in _call_with_fallback.</t>
+          <t>Regression for prod appointment 426. Fixed via _sanitize_user_field ascii-strip; UnicodeEncodeError short-circuit in factory._try_backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>CI-84</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Summariser resilience</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Persist path survives Vertex-refactor: _model_name compat shim</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit any appointment (Tamil or English name)
+2. Wait 10s for background summarisation
+3. Check log for '[GEMINI WARN] ... has no attribute _model_name'
+4. Verify GrievanceSummaryRecord row exists with gemini_model_used populated</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>NO 'has no attribute _model_name' error in log; DB row exists with gemini_model_used = primary model name (e.g. 'gemini-2.5-flash')</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Regression for prod appointment 430 after ca5d82a Vertex-first refactor. Fixed by _model_name @property on GrievanceSummarisationService + PetitionExtractionService returning self._bundle.primary_model.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I84"/>
+  <autoFilter ref="A1:I85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4210,8 +4210,98 @@
         </is>
       </c>
     </row>
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>CI-85</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Referral form — behavior</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Invalid mobile → red inline hint under mobile field (not just top banner)</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /referral in Tamil mode
+2. Fill valid name + shared-by + 5-word reason + slot
+3. Type '971022517' (9 digits) in mobile
+4. Try to submit</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Hint 'Enter a valid 10-digit mobile...' under the mobile field turns RED, submit is blocked, mobile field is focused. NO generic 'பதிவு தோல்வி' banner without explanation.</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>USER-REPORTED: only the generic 'Booking failed' banner shown, no inline field-level error. Fixed by adding _mobileOk() + mobileHint div + client-side submit guard mirroring the reasonHint pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>CI-86</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Referral form — behavior</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Slot chips never leak remaining capacity ('N மீதம்' / 'N left')</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /referral, pick a date with partially-booked slots
+2. Inspect each open slot chip</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Available slots show ONLY the time range (no 'N மீதம்' / 'N left' text). Past slots still say 'முடிந்தது' / 'Passed', full slots say 'நிரம்பியது' / 'Full'.</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>USER-REQUESTED: don't reveal office capacity to citizens. Fixed in referral_form.jinja2 partial branch of slot render + _relabelSlots. form.jinja2 already correct.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I85"/>
+  <autoFilter ref="A1:I87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4300,8 +4300,98 @@
         </is>
       </c>
     </row>
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>CI-87</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Referral form — behavior</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Backend validation errors surface the SPECIFIC reason (not generic 'Booking failed')</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>1. /referral in Tamil mode
+2. Paste ~5000 chars into 'சந்திப்பின் காரணம்' (server max is 500)
+3. Fill other fields validly, pick slot, submit</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Banner shows 'காரணம் அதிகபட்சம் 500 எழுத்துகள் மட்டுமே அனுமதிக்கப்படும்.' (or English equivalent), reasonHint turns red. NOT a bare 'பதிவு தோல்வி' with no explanation. Live counter under reason shows '5000 / 500' in red before submit.</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr"/>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>USER-REPORTED: FastAPI validation returns {detail: [...]} but frontend read {error: ...}. Fixed via _humanErrorFromResponse mapper + maxlength on all text fields + reasonCount live counter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>CI-88</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Upload / AI</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>QR intake form — backend errors show specific reason (form.jinja2 parity)</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>1. Complete QR intake up to submit step
+2. Trigger any backend validation failure (huge description, blank required, etc.)
+3. Observe error surface</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>showOtpFieldError shows a specific localized message (e.g. 'Field can be at most N characters.'). NOT '[object Object]' and NOT a bare 'Submission failed.'</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr"/>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>form.jinja2 had the same bug — `error.detail || copy.submitError` treated an array as a string. Fixed with same detail[0] type-based mapper as referral form.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I87"/>
+  <autoFilter ref="A1:I89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4390,8 +4390,52 @@
         </is>
       </c>
     </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>CI-89</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Upload / AI</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Citizen document iframe preview renders (not 'blocked:other')</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>1. Portal → Tickets → open a ticket with a PDF upload (e.g. TKN2026082300006)
+2. Inspect the drawer's document preview + DevTools Network tab</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>PDF renders inside the drawer's &lt;iframe&gt;. Network row for /dashboard/api/files/... shows 200 (not 'blocked:other'). Response headers on the file: X-Frame-Options: SAMEORIGIN, Content-Security-Policy contains 'frame-ancestors ...'.</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>USER-REPORTED: 'documents are blocked'. Fixed by scoping the middleware's XFO DENY + frame-ancestors 'none' to skip /dashboard|events|minister|department/api/files/* (see backend/src/main.py _EMBEDDABLE_PREFIXES). frame-ancestors uses CORS_ORIGINS for split-origin deploys.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I89"/>
+  <autoFilter ref="A1:I90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,12 @@
       <b val="1"/>
       <color rgb="005B21B6"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00166534"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +127,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -573,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -603,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +655,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -654,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
     </row>
@@ -672,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4422,20 +4434,114 @@
           <t>PDF renders inside the drawer's &lt;iframe&gt;. Network row for /dashboard/api/files/... shows 200 (not 'blocked:other'). Response headers on the file: X-Frame-Options: SAMEORIGIN, Content-Security-Policy contains 'frame-ancestors ...'.</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>PASS on Railway after cache-disabled reload — user confirmed 'now working'. Immutable cache from the pre-fix response was the initial red herring; hard reload with DevTools cache-disabled surfaced the SAMEORIGIN headers and the drawer PDF preview started rendering.</t>
+        </is>
+      </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
           <t>USER-REPORTED: 'documents are blocked'. Fixed by scoping the middleware's XFO DENY + frame-ancestors 'none' to skip /dashboard|events|minister|department/api/files/* (see backend/src/main.py _EMBEDDABLE_PREFIXES). frame-ancestors uses CORS_ORIGINS for split-origin deploys.</t>
         </is>
       </c>
     </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>CI-90</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting UX</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>QR success page auto-downloads receipt PNG on load</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>1. Complete a QR-scan submission end-to-end (any citizen, any language)
+2. Land on /form/success?token=...
+3. Wait ~1s and check the browser's /Downloads folder</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>File 'grievance-TKN&lt;token&gt;.png' auto-saves. Filename contains ONLY the token (NEVER the citizen's name). The Download button in the top-right of the card still works for manual re-save.</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>USER-REQUESTED (option 3 of the CITZ-13 revisit): auto-download but with token-only filename so shared/kiosk devices don't leak identity. Enabled via setTimeout(downloadCard(true), 400) in success.jinja2 DOMContentLoaded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>CI-91</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting UX</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Referral success page auto-downloads receipt PNG + shows Download button</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>1. Complete a valid /referral submission
+2. Wait for the success box to appear
+3. Watch /Downloads (auto) and try the visible 'Download receipt' button</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>File 'referral-REF&lt;token&gt;.png' auto-saves. Manual Download button in the success box also produces the same PNG. Both filenames token-only (no cleartext citizen name in the filename).</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>USER-REQUESTED: parity with QR success. Vendored html2canvas already available at /static/assets/vendor/. New downloadReferralCard() + auto-trigger + button added to referral_form.jinja2.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I90"/>
+  <autoFilter ref="A1:I92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,7 +47,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00374151"/>
+      <color rgb="00166534"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +55,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00166534"/>
+      <color rgb="00374151"/>
     </font>
   </fonts>
   <fills count="6">
@@ -72,7 +72,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
+        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,7 +82,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6fda89b</t>
+          <t>f742c13</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P1 — Citizen Intake</t>
+          <t>P2 — PA Petition Review</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>55%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -780,10 +780,14 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -821,10 +825,14 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -862,10 +870,14 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -903,10 +915,14 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -944,10 +960,14 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -984,10 +1004,14 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -1024,10 +1048,14 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -1064,10 +1092,14 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -1104,10 +1136,14 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Design decision — must not silently save '+91' inside stored mobile</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -1188,10 +1228,14 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -1228,10 +1272,14 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -1268,10 +1316,14 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -1308,10 +1360,14 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -1348,10 +1404,14 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -1388,10 +1448,14 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -1429,10 +1493,14 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>XSS regression</t>
@@ -1473,10 +1541,14 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -1514,10 +1586,14 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>CITZ-03 Critical fix</t>
@@ -1559,10 +1635,14 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
@@ -1600,10 +1680,14 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
@@ -1641,10 +1725,14 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
@@ -1729,10 +1817,14 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
@@ -1769,10 +1861,14 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
@@ -1809,10 +1905,14 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
@@ -1849,10 +1949,14 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
@@ -1889,10 +1993,14 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
@@ -1929,10 +2037,14 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>iOS default format — must not silently fail</t>
@@ -1973,10 +2085,14 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
@@ -2013,10 +2129,14 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -2052,10 +2172,14 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>SVG can carry JS — must be rejected</t>
@@ -2096,10 +2220,14 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="60" customHeight="1">
@@ -2136,10 +2264,14 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="60" customHeight="1">
@@ -2176,10 +2308,14 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="60" customHeight="1">
@@ -2216,10 +2352,14 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I37" s="5" t="inlineStr"/>
     </row>
     <row r="38" ht="60" customHeight="1">
@@ -2258,10 +2398,14 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>CITZ-02 Critical XSS fix</t>
@@ -2303,10 +2447,14 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="60" customHeight="1">
@@ -2344,10 +2492,14 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="60" customHeight="1">
@@ -2384,10 +2536,14 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="60" customHeight="1">
@@ -2424,10 +2580,14 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="60" customHeight="1">
@@ -2464,10 +2624,14 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr"/>
     </row>
     <row r="44" ht="60" customHeight="1">
@@ -2504,10 +2668,14 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I44" s="5" t="inlineStr"/>
     </row>
     <row r="45" ht="60" customHeight="1">
@@ -2545,10 +2713,14 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="60" customHeight="1">
@@ -2585,10 +2757,14 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="60" customHeight="1">
@@ -2625,10 +2801,14 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Verifies businessMessage() TECHNICAL regex</t>
@@ -2669,10 +2849,14 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="60" customHeight="1">
@@ -2709,10 +2893,14 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="60" customHeight="1">
@@ -2749,10 +2937,14 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="60" customHeight="1">
@@ -2789,10 +2981,14 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="60" customHeight="1">
@@ -2829,10 +3025,14 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway — 'Vertex AI backend ready (project=namkural location=asia-south1 creds=env-content)' in appointment 430 log</t>
+        </is>
+      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Verifies petition_extraction.py Vertex overload (commit 6fda89b)</t>
@@ -2873,10 +3073,14 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr"/>
     </row>
     <row r="54" ht="60" customHeight="1">
@@ -2913,10 +3117,14 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Verifies event_service.py _ascii_safe fix</t>
@@ -2957,10 +3165,14 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr"/>
     </row>
     <row r="56" ht="60" customHeight="1">
@@ -2997,10 +3209,14 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="60" customHeight="1">
@@ -3037,10 +3253,14 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr"/>
     </row>
     <row r="58" ht="60" customHeight="1">
@@ -3077,10 +3297,14 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="60" customHeight="1">
@@ -3117,10 +3341,14 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr"/>
     </row>
     <row r="60" ht="60" customHeight="1">
@@ -3155,7 +3383,7 @@
           <t>Two independent tickets, both AWAITING_REVIEW; both appointments visible</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3163,7 +3391,7 @@
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Setup for CI-60/61</t>
+          <t>Setup for CI-60/61. Awaiting focused end-to-end pass — reported-bug regression.</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3427,7 @@
           <t>Petition row created; A's appointment still linked; ticket advances</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3239,7 +3467,7 @@
           <t>Either merges into A's signatory list WITH B's appointment PRESERVED, OR creates B as separate petition. B's appointment must not vanish.</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3247,7 +3475,7 @@
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>USER-REPORTED BUG: 'appointment gone and not found in the petition too'</t>
+          <t>USER-REPORTED BUG: 'appointment gone and not found in the petition too'. Focus of the dedup pass.</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3511,7 @@
           <t>Second recognized as same citizen (mobile blind index match); either updates name or flags conflict; no duplicate citizen row</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3327,7 +3555,7 @@
           <t>Recognized as same citizen; name normalization consistent</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3367,7 +3595,7 @@
           <t>Both persisted OR one wins with clean dedup; no orphan rows, no partial state, no double-commit</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -3414,10 +3642,14 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
           <t>Verifies PERF-18 Cache-Control on /api/venues</t>
@@ -3458,10 +3690,14 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr"/>
     </row>
     <row r="68" ht="60" customHeight="1">
@@ -3498,10 +3734,14 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="60" customHeight="1">
@@ -3537,10 +3777,14 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr"/>
     </row>
     <row r="70" ht="60" customHeight="1">
@@ -3578,10 +3822,14 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
           <t>Related to CI-61 bug</t>
@@ -3622,15 +3870,15 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Active test in current env</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway — guard off in current test window</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr"/>
     </row>
     <row r="72" ht="60" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -3715,10 +3963,14 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>CITZ-01 Critical</t>
@@ -3759,10 +4011,14 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="60" customHeight="1">
@@ -3800,10 +4056,14 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I75" s="5" t="inlineStr"/>
     </row>
     <row r="76" ht="60" customHeight="1">
@@ -3841,10 +4101,14 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="60" customHeight="1">
@@ -3882,10 +4146,14 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr"/>
     </row>
     <row r="78" ht="60" customHeight="1">
@@ -3922,10 +4190,14 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Regression net for TECHNICAL regex + businessMessage()</t>
@@ -3966,10 +4238,14 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I79" s="5" t="inlineStr"/>
     </row>
     <row r="80" ht="60" customHeight="1">
@@ -4006,10 +4282,14 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="60" customHeight="1">
@@ -4046,10 +4326,14 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I81" s="5" t="inlineStr"/>
     </row>
     <row r="82" ht="60" customHeight="1">
@@ -4086,10 +4370,14 @@
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="60" customHeight="1">
@@ -4125,10 +4413,14 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I83" s="5" t="inlineStr"/>
     </row>
     <row r="84" ht="60" customHeight="1">
@@ -4155,7 +4447,7 @@
       <c r="E84" s="5" t="inlineStr">
         <is>
           <t>1. Submit an appointment where citizen name field contains Tamil (e.g. 'ராம் குமார்')
-2. Wait 10s for the background summariser (spawn_bg → _trigger_summarisation)
+2. Wait 10s for the background summariser
 3. Tail Railway logs OR open the appointment's GrievanceSummaryRecord in the portal</t>
         </is>
       </c>
@@ -4166,10 +4458,14 @@
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
           <t>Regression for prod appointment 426. Fixed via _sanitize_user_field ascii-strip; UnicodeEncodeError short-circuit in factory._try_backend.</t>
@@ -4212,10 +4508,14 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>Regression for prod appointment 430 after ca5d82a Vertex-first refactor. Fixed by _model_name @property on GrievanceSummarisationService + PetitionExtractionService returning self._bundle.primary_model.</t>
@@ -4258,13 +4558,17 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>USER-REPORTED: only the generic 'Booking failed' banner shown, no inline field-level error. Fixed by adding _mobileOk() + mobileHint div + client-side submit guard mirroring the reasonHint pattern.</t>
+          <t>USER-REPORTED. Fixed by adding _mobileOk() + mobileHint div + client-side submit guard.</t>
         </is>
       </c>
     </row>
@@ -4302,13 +4606,17 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>USER-REQUESTED: don't reveal office capacity to citizens. Fixed in referral_form.jinja2 partial branch of slot render + _relabelSlots. form.jinja2 already correct.</t>
+          <t>USER-REQUESTED: don't reveal office capacity to citizens.</t>
         </is>
       </c>
     </row>
@@ -4347,10 +4655,14 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
           <t>USER-REPORTED: FastAPI validation returns {detail: [...]} but frontend read {error: ...}. Fixed via _humanErrorFromResponse mapper + maxlength on all text fields + reasonCount live counter.</t>
@@ -4392,10 +4704,14 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
           <t>form.jinja2 had the same bug — `error.detail || copy.submitError` treated an array as a string. Fixed with same detail[0] type-based mapper as referral form.</t>
@@ -4434,19 +4750,19 @@
           <t>PDF renders inside the drawer's &lt;iframe&gt;. Network row for /dashboard/api/files/... shows 200 (not 'blocked:other'). Response headers on the file: X-Frame-Options: SAMEORIGIN, Content-Security-Policy contains 'frame-ancestors ...'.</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="G90" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
-          <t>PASS on Railway after cache-disabled reload — user confirmed 'now working'. Immutable cache from the pre-fix response was the initial red herring; hard reload with DevTools cache-disabled surfaced the SAMEORIGIN headers and the drawer PDF preview started rendering.</t>
+          <t>PASS on Railway after cache-disabled reload — user confirmed 'now working'.</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>USER-REPORTED: 'documents are blocked'. Fixed by scoping the middleware's XFO DENY + frame-ancestors 'none' to skip /dashboard|events|minister|department/api/files/* (see backend/src/main.py _EMBEDDABLE_PREFIXES). frame-ancestors uses CORS_ORIGINS for split-origin deploys.</t>
+          <t>USER-REPORTED. Fixed by scoping the middleware's XFO DENY + frame-ancestors 'none' to skip /dashboard|events|minister|department/api/files/*.</t>
         </is>
       </c>
     </row>
@@ -4485,13 +4801,17 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>USER-REQUESTED (option 3 of the CITZ-13 revisit): auto-download but with token-only filename so shared/kiosk devices don't leak identity. Enabled via setTimeout(downloadCard(true), 400) in success.jinja2 DOMContentLoaded.</t>
+          <t>USER-REQUESTED (option 3 of the CITZ-13 revisit): auto-download but with token-only filename so shared/kiosk devices don't leak identity.</t>
         </is>
       </c>
     </row>
@@ -4530,18 +4850,2550 @@
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>USER-REQUESTED: parity with QR success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>PR-01</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Access / RBAC</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>pa_admin can load /ai-review</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as admin-office (pa_admin role)
+2. Navigate to /ai-review</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Page loads; AWAITING_REVIEW list visible; no 403 / login redirect</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>USER-REQUESTED: parity with QR success. Vendored html2canvas already available at /static/assets/vendor/. New downloadReferralCard() + auto-trigger + button added to referral_form.jinja2.</t>
-        </is>
-      </c>
+      <c r="H93" s="5" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>PR-02</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Access / RBAC</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>dept_officer redirected AWAY from /ai-review</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as a dept_officer account
+2. Try /ai-review directly</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Redirect to /tickets (or 403); no AWAITING_REVIEW list visible; _no_dept_officer gate honoured</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Verifies dashboard.py _no_dept_officer dependency</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>PR-03</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Access / RBAC</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Unauthenticated → redirect to /auth/login</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>1. Wipe dash_session cookie
+2. Navigate to /ai-review</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Clean 302 to /auth/login; no traceback; no data leaked</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr"/>
+      <c r="I95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>PR-04</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Access / RBAC</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Tampered dash_session cookie → 401 / login</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. In devtools, change one char of the session cookie
+3. Reload /ai-review</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Session invalidated; polite redirect / message; no server 500</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>PR-05</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>List &amp; counts</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Empty state when no AWAITING_REVIEW rows</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>1. Fresh test env with zero AWAITING_REVIEW appointments
+2. Load /ai-review</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Friendly empty-state ('All caught up' or similar); no undefined / broken layout; no error toast</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>PR-06</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>List &amp; counts</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Default list shows AWAITING_REVIEW only (not SCHEDULED / REVIEWED)</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>1. Seed appointments in SCHEDULED / AWAITING_REVIEW / REVIEWED
+2. Load /ai-review with default filter</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Only AWAITING_REVIEW rows appear. SCHEDULED lives in /appointments; REVIEWED lives in Tickets.</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr"/>
+      <c r="I98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>PR-07</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>List &amp; counts</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Counts bar matches /api/appointments/counts</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>1. Note the count pills at the top (Total / Today / This week / whatever the header shows)
+2. Compare to a direct GET /dashboard/api/appointments/counts response</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Numbers match exactly. No off-by-one from timezone (IST vs UTC).</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr"/>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Verifies IST/UTC drift fix (CORR-07/08/09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>PR-08</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>List &amp; counts</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Fresh submission appears after refresh/poll</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>1. Load /ai-review (note current count N)
+2. In another tab, submit a citizen petition
+3. Return to /ai-review; wait for the polling interval</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>New row appears without a full page reload; count → N+1</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>PR-09</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Category filter narrows list</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>1. Pick 'action_required' from Category filter
+2. Verify row set</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Only action_required rows visible; count pill updates; URL reflects the filter</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr"/>
+      <c r="I101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>PR-10</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Priority filter narrows list</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>1. Pick 'high' priority
+2. Verify</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Only high-priority rows visible; empty-state if none</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>PR-11</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Ministry filter narrows list</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>1. Pick a ministry
+2. Verify row set</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Only rows for that ministry (from GrievanceSummaryRecord); rows without a GSR are excluded cleanly</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr"/>
+      <c r="I103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>PR-12</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Submission date range filter</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>1. Set date_from = today, date_to = today
+2. Verify</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Only appointments submitted today (IST) shown</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr"/>
+      <c r="I104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>PR-13</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Appointment (meeting) date filter</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>1. Set appt_date_from / appt_date_to to tomorrow
+2. Verify</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Only appointments with a scheduled slot tomorrow — filters on MLADailyAvailability.date, not created_at</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr"/>
+      <c r="I105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>PR-14</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Venue filter (exact match on VenueRegistry.key)</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>1. Pick a venue
+2. Verify</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Only rows whose Appointment.venue_id equals that key; historical rows for deactivated venues still match by key</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr"/>
+      <c r="I106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>PR-15</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Search by citizen name (substring)</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>1. Type a citizen's name in search
+2. Verify</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Rows whose decrypted citizen name contains the substring (case-insensitive)</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr"/>
+      <c r="I107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>PR-16</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Search by mobile (last-4 or full number)</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>1. Search '3210' (last 4 of citizen mobile)
+2. Search full 10-digit mobile</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Both find the citizen. Uses blind-index for full mobile; last-N substring against masked format for last-4.</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr"/>
+      <c r="I108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>PR-17</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Search by token number</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>1. Search 'TKN2026...' or bare digits
+2. Verify</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Row with that token appears at top; other rows filtered out</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr"/>
+      <c r="I109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>PR-18</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Clear-all filters resets to default</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>1. Apply 3+ filters
+2. Click Reset / Clear all</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>All filters removed; list returns to full AWAITING_REVIEW view; URL cleaned</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr"/>
+      <c r="I110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>PR-19</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Sort &amp; pagination</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Default sort (newest submissions first)</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>1. Load /ai-review (no sort override)
+2. Compare row order to created_at DESC</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Newest at top; deterministic tie-break by id (PERF-08 fix)</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr"/>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Verifies PERF-08 id tie-break on paginated ORDER BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>PR-20</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Sort &amp; pagination</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Sort by urgency (CRITICAL &gt; HIGH &gt; MEDIUM &gt; LOW)</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>1. Choose urgency sort
+2. Verify order</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL rows first, then HIGH, MEDIUM, LOW. Ties broken by created_at DESC + id.</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr"/>
+      <c r="I112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>PR-21</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Sort &amp; pagination</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Pagination — page 2 loads next set</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>1. Seed &gt;25 AWAITING_REVIEW rows
+2. Load /ai-review; verify page 1
+3. Go to page 2</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Page 2 has correct next-25; no duplicates; count / total consistent with counts endpoint</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr"/>
+      <c r="I113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>PR-22</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Drawer opens on row click; URL updates with token</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>1. Click any row
+2. Verify drawer + URL</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Drawer slides in; URL updates with ?ticket=&lt;id&gt; or similar; browser back closes it</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr"/>
+      <c r="I114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>PR-23</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Deep-link to a specific ticket opens the drawer</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /ai-review?ticket=&lt;id&gt; directly in a fresh tab</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Page loads with drawer already open on the specified row</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr"/>
+      <c r="I115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>PR-24</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Citizen name / mobile (masked) / constituency / district all shown</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer
+2. Scan the OVERVIEW panel</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>All four fields present. Mobile shown as ******3210 (mask), not raw. Constituency / district reflect what was extracted / entered.</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr"/>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Verifies mask_mobile helper — must never show raw mobile in drawer</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>PR-25</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Category / priority / ministry badges render with correct colours</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer
+2. Screenshot the badge row</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Category pill, priority pill (colour-coded LOW/MEDIUM/HIGH/CRITICAL), ministry pill. Values match GrievanceSummaryRecord.</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>PR-26</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>AI summary text renders (English + Tamil, no mojibake)</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer where GrievanceSummaryRecord.summary_ta is populated
+2. Toggle language
+3. Verify Tamil renders in Noto Serif Tamil, English in Inter</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Bilingual summary. No ??? or garbled bytes. Bullets render as bullets.</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>PR-27</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Key details bullets render</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer with key_details populated
+2. Scan the section</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Bullet list of concrete evidence (dates, amounts, section citations, prior escalation)</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr"/>
+      <c r="I119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>PR-28</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Citizen uploads section count matches attachments</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer
+2. Compare the 'CITIZEN UPLOADS N' chip to actual attachment count</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>N equals AppointmentAttachment row count; DOC / IMG / AUDIO badges reflect actual mime types</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr"/>
+      <c r="I120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>PR-29</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>PDF renders inline in iframe (regression for CI-89)</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer for a ticket with a PDF upload
+2. Verify the PDF renders inside the preview</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Not 'blocked:other'. XFO SAMEORIGIN + frame-ancestors 'self' honoured. Same behaviour as CI-89 but exercised from Petition Review, not Tickets.</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Regression for iframe preview fix (commit 38a64bc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>PR-30</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Audio playback works (native &lt;audio&gt; controls + seek)</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer for a ticket with a voice recording
+2. Play the audio; drag the seek bar</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Native &lt;audio&gt; renders duration correctly (Range requests supported); seek jumps to arbitrary position; no infinite duration on WebM/Opus</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Verifies Range request handling in serve_stored_file</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>PR-31</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Drawer closes via X button + Esc key</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>1. Open drawer
+2. Press Escape
+3. Reopen; click the X</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Both close the drawer; URL cleaned; row loses selected state</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr"/>
+      <c r="I123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>PR-32</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Approve</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Approve creates a Ticket row</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer
+2. Click Approve
+3. Verify DB / Tickets tab</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>New row in tickets table; ticket.appointment_id = appt.id; ticket.status = OPEN</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>PR-33</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Approve</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Ticket number generated correctly (year-count)</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve N appointments in a row
+2. Check ticket_number pattern</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>TKN&lt;year&gt;&lt;ordinal&gt; format (e.g. TKN2026082300007). Monotonically increasing within the year; no gaps from failed inserts.</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>PR-34</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Approve</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Appointment.status flips to REVIEWED</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve a drawer
+2. Refetch the appointment</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>appt.status = 'REVIEWED'; visible in /appointments 'Reviewed' filter</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr"/>
+      <c r="I126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>PR-35</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Approve</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Drawer transitions to a 'Ticket created' success state</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve
+2. Watch the drawer</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Approve button becomes success chip / link to new ticket. Row disappears from AWAITING_REVIEW list (either optimistically or after refresh).</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>PR-36</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Approve</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>SMS notification triggered on approve (visible in logs)</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve a drawer with a citizen mobile
+2. Tail Railway logs for the SMS dispatch line</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>spawn_bg(_notify(kind='convert_to_petition', ...)) fires; log line 'SMS dispatched' or MSG91 stub log (no real send in test env)</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr"/>
+      <c r="I128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>PR-37</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Approve</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Activity log records 'created' event with actor + payload</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve a drawer
+2. Open the activity log on the resulting ticket</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Activity row: action_type='created', user='pa_admin', message references the token, payload has {token, appointment_id}</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr"/>
+      <c r="I129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>PR-38</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Approve</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Approve is idempotent — double-click doesn't create two tickets</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>1. Rapidly click Approve twice
+2. Check tickets table</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>One ticket only. Button disabled during in-flight submit. No 500. No orphan appointment status.</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr"/>
+      <c r="I130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>PR-39</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Dismiss</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Dismiss requires a reason (or explicit confirmation)</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer
+2. Click Dismiss without a reason</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Prompted for a reason OR confirmation modal. Cancel returns to drawer without change.</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>PR-40</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Dismiss</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Dismissed appointment removed from default list, added to DISMISSED bucket</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>1. Dismiss a row
+2. Verify default list + DISMISSED filter</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Row leaves the default (AWAITING_REVIEW) view; visible under a DISMISSED filter / status; appt.status = 'DISMISSED'</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr"/>
+      <c r="I132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>PR-41</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Dismiss</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Restore endpoint sends back to AWAITING_REVIEW</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a DISMISSED row
+2. Click Restore</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>appt.status → 'AWAITING_REVIEW'; row reappears in default list; activity log records 'restored'</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr"/>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Verifies /api/appointments/{id}/restore endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>PR-42</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Triage — Dismiss</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Activity log records dismiss + reason</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>1. Dismiss with reason 'duplicate submission'
+2. Open activity log</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Activity row with action_type='dismissed', reason preserved in payload</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr"/>
+      <c r="I134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>PR-43</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Manual edits</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Edit citizen name (PATCH /details) persists</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>1. Click edit pencil on citizen name
+2. Change name; save
+3. Refresh drawer</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Name updated on citizen row (encrypted + blind-index rehashed). Drawer shows the new value.</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr"/>
+      <c r="I135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>PR-44</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Manual edits</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Edit constituency persists</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>1. Edit constituency; save
+2. Refresh drawer</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>New value persisted on Appointment row</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr"/>
+      <c r="I136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>PR-45</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Manual edits</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Edit category persists + reflects in filter immediately</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>1. Change category from 'other' to 'action_required'
+2. Apply category=action_required filter</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Row now included in the filtered list; category badge updated in the drawer</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>PR-46</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Manual edits</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Edit priority overrides AI-inferred value</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>1. AI set priority=MEDIUM; PA changes to HIGH
+2. Save; refresh</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>GrievanceSummaryRecord (or appt override field) shows HIGH; badge colour updated; sort-by-urgency respects the override</t>
+        </is>
+      </c>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>PR-47</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Manual edits</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Edit ministry persists + reflects in ministry filter</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>1. Change ministry to a different one; save
+2. Apply filter for the new ministry</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Row appears in the new bucket, disappears from the old</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>PR-48</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Manual edits</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Edit conflict — two tabs — last-write-wins with clean UI</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the same drawer in two tabs
+2. Edit + save in Tab A
+3. Edit + save in Tab B (without refreshing)</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Second save either succeeds (overwrites) with a clear indicator, OR is rejected with a polite 'this ticket was updated elsewhere — refresh' message. No silent 500 / no lost data.</t>
+        </is>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>PR-49</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Attachments</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>PA adds an attachment from drawer — uploads OK + count increments</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer
+2. Use the Add attachment control; upload a small PDF</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/appointments/{id}/attachment succeeds; CITIZEN UPLOADS count +1; new chip visible; file preview works</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>PR-50</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Attachments</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Attachment respects 5MB size cap + 10-file total cap</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>1. Try uploading a 6MB file → expect reject
+2. When appt already has 10 attachments → try one more → expect reject</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Clean 413 or client-side block with human message; server-side cap honoured; count never exceeds 10</t>
+        </is>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr"/>
+      <c r="I142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>PR-51</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Attachments</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Filename XSS (regression for CITZ-02) in Petition Review drawer</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>1. Upload a PDF renamed to '&lt;script&gt;alert(1)&lt;/script&gt;.pdf' via PA drawer
+2. Inspect chip render</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Filename escaped in drawer chip AND in file preview title. No alert dialog. No console error.</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>CITZ-02 regression from the drawer surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>PR-52</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Signatory dedup</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Similar-cases endpoint returns close matches</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer
+2. GET /api/appointments/{id}/similar</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Returns candidate AWAITING_REVIEW rows blocked by category + district, scored by normalized similarity</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr"/>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>Verifies /similar endpoint added for merge suggestions</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>PR-53</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Signatory dedup</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Approve-with-signatories merges into an existing petition</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a drawer with a similar case
+2. Approve-with-signatories → target an existing ticket</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Current appt merged as a signatory of the target ticket. No new Ticket row. Both citizens visible on the merged ticket's signatory list.</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr"/>
+      <c r="I145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>PR-54</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Signatory dedup</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Merge preserves original citizen's appointment (Phase 1 CI-61 regression)</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>1. Follow the CI-61 scenario end-to-end via the merge flow
+2. Verify both appointments after merge</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Both citizens' appointments remain linked. Neither disappears. USER-REPORTED bug from Phase 1 stays fixed via the Petition Review path too.</t>
+        </is>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>PR-55</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Signatory dedup</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Concurrent merge (two PAs) — FOR UPDATE lock prevents ghost rows</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>1. Two PAs open the same drawer
+2. Both click Approve-with-signatories on the same target within 1s</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>One wins; the other gets a clean 'already merged / target updated' message. No duplicate signatory row. No partial state.</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr"/>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>Verifies CORR-06 FOR UPDATE row-lock on signatory merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>PR-56</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Signatory dedup</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Cross-department merge respects RBAC gate</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>1. As pa_admin scoped to Dept A, try to merge into a target that lives in Dept B
+2. Verify behavior</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Either allowed with a warning, OR blocked with a clean 'target belongs to another department' message. Never a silent cross-department mutation.</t>
+        </is>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr"/>
+      <c r="I148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>PR-57</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>PA can add a comment via drawer — persists + shows in activity log</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>1. Add a comment via /api/appointments/{id}/comment
+2. Reload the drawer / activity log</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Comment stored; visible in the activity feed with author + timestamp</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>PR-58</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Comment supports Tamil characters (no ??? or codec error)</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>1. Add a Tamil comment: 'மீண்டும் அழைக்கவும்'
+2. Reload</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Tamil preserved end-to-end. No mojibake. No SDK ascii-in-header error (comment path is DB only, not Gemini — so no expected failure).</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr"/>
+      <c r="I150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>PR-59</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting UX</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>All error toasts polished across Petition Review</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>1. Trigger errors: 5MB+ attachment, network offline mid-approve, backend 500, invalid edit
+2. Screenshot each toast</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Zero tracebacks. Zero 'gemini-2.5-flash'. Zero raw HTTP codes. All messages routed through businessMessage() (frontend errors.ts).</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr"/>
+      <c r="I151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>PR-60</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting UX</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Loading skeleton on drawer open (&gt;200ms fetch)</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>1. Throttle network to 'Slow 3G' in devtools
+2. Open a drawer</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Skeleton / spinner visible while fetching. No content flash. No blank white area.</t>
+        </is>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr"/>
+      <c r="I152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>PR-61</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting UX</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>Mobile viewport (375px) — drawer usable, no horizontal scroll</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>1. Resize to 375x812
+2. Open a drawer</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Drawer either becomes a full-screen sheet or scales down. All actions reachable with thumbs. No horizontal scroll on body.</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>PR-62</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting UX</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Polling refresh — new petitions appear without full page reload</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>1. Load /ai-review; note current count
+2. In another tab / device, submit a new petition
+3. Wait for the polling interval</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>New row appears in the list; count updates. No full-page refresh needed. Drawer content preserved if open on a different row.</t>
+        </is>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I92"/>
+  <autoFilter ref="A1:I154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f742c13</t>
+          <t>4a26213</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>153</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -666,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4877,23 +4877,23 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Access / RBAC</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>pa_admin can load /ai-review</t>
+          <t>RBAC — pa_admin loads, dept_officer redirects</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>1. Log in as admin-office (pa_admin role)
-2. Navigate to /ai-review</t>
+          <t>1. Log in as pa_admin (admin-office) → /ai-review
+2. Log in as dept_officer → /ai-review</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Page loads; AWAITING_REVIEW list visible; no 403 / login redirect</t>
+          <t>pa_admin sees the list. dept_officer redirected to /tickets (per _no_dept_officer gate).</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -4917,23 +4917,23 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Access / RBAC</t>
+          <t>Access</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>dept_officer redirected AWAY from /ai-review</t>
+          <t>Unauth / tampered session → clean login redirect</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>1. Log in as a dept_officer account
-2. Try /ai-review directly</t>
+          <t>1. Wipe or corrupt dash_session cookie
+2. Load /ai-review</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Redirect to /tickets (or 403); no AWAITING_REVIEW list visible; _no_dept_officer gate honoured</t>
+          <t>302 to /auth/login; no traceback; no data leaked</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
@@ -4942,11 +4942,7 @@
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Verifies dashboard.py _no_dept_officer dependency</t>
-        </is>
-      </c>
+      <c r="I94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="60" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -4961,23 +4957,23 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Access / RBAC</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Unauthenticated → redirect to /auth/login</t>
+          <t>Default list = AWAITING_REVIEW only</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>1. Wipe dash_session cookie
-2. Navigate to /ai-review</t>
+          <t>1. Seed rows in SCHEDULED / AWAITING_REVIEW / REVIEWED
+2. Load /ai-review</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Clean 302 to /auth/login; no traceback; no data leaked</t>
+          <t>Only AWAITING_REVIEW rows appear. Empty-state is friendly when count is zero.</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
@@ -5001,24 +4997,24 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Access / RBAC</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Tampered dash_session cookie → 401 / login</t>
+          <t>Filter + search + sort work</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>1. Log in
-2. In devtools, change one char of the session cookie
-3. Reload /ai-review</t>
+          <t>1. Apply category filter → verify
+2. Search by name / mobile last-4 / token → verify
+3. Switch to urgency sort → verify order (CRITICAL &gt; HIGH &gt; MED &gt; LOW)</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Session invalidated; polite redirect / message; no server 500</t>
+          <t>Each control narrows the list correctly. Newest-first default has an id tie-break (PERF-08). Clear-all restores.</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
@@ -5042,23 +5038,24 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>List &amp; counts</t>
+          <t>List</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Empty state when no AWAITING_REVIEW rows</t>
+          <t>Pagination + counts match /counts endpoint</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>1. Fresh test env with zero AWAITING_REVIEW appointments
-2. Load /ai-review</t>
+          <t>1. Seed &gt;25 rows
+2. Load page 1, then page 2
+3. Compare visible total to GET /dashboard/api/appointments/counts</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Friendly empty-state ('All caught up' or similar); no undefined / broken layout; no error toast</t>
+          <t>Page 2 shows next 25 (no dupes). Counts match exactly (no IST/UTC drift). Fresh submission appears after the polling interval.</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
@@ -5082,23 +5079,24 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>List &amp; counts</t>
+          <t>Drawer</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Default list shows AWAITING_REVIEW only (not SCHEDULED / REVIEWED)</t>
+          <t>Drawer opens on click + deep-link</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>1. Seed appointments in SCHEDULED / AWAITING_REVIEW / REVIEWED
-2. Load /ai-review with default filter</t>
+          <t>1. Click a row → verify drawer + URL update
+2. Open /ai-review?ticket=&lt;id&gt; in a fresh tab
+3. Close via X + Esc</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Only AWAITING_REVIEW rows appear. SCHEDULED lives in /appointments; REVIEWED lives in Tickets.</t>
+          <t>Both entry points open the drawer with the right row. X and Esc close it. Browser back closes it too.</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
@@ -5122,23 +5120,23 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>List &amp; counts</t>
+          <t>Drawer</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Counts bar matches /api/appointments/counts</t>
+          <t>Overview panel — name, masked mobile, badges</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>1. Note the count pills at the top (Total / Today / This week / whatever the header shows)
-2. Compare to a direct GET /dashboard/api/appointments/counts response</t>
+          <t>1. Open drawer
+2. Scan the OVERVIEW panel</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Numbers match exactly. No off-by-one from timezone (IST vs UTC).</t>
+          <t>Name / masked mobile (******3210) / constituency / district present. Category + priority (colour-coded) + ministry pills reflect GSR.</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -5149,7 +5147,7 @@
       <c r="H99" s="5" t="inlineStr"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Verifies IST/UTC drift fix (CORR-07/08/09)</t>
+          <t>Mobile mask regression</t>
         </is>
       </c>
     </row>
@@ -5166,24 +5164,23 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>List &amp; counts</t>
+          <t>Drawer</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Fresh submission appears after refresh/poll</t>
+          <t>Bilingual summary + key details render (no mojibake)</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>1. Load /ai-review (note current count N)
-2. In another tab, submit a citizen petition
-3. Return to /ai-review; wait for the polling interval</t>
+          <t>1. Open a drawer with Tamil summary_ta + key_details_ta populated
+2. Toggle language</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>New row appears without a full page reload; count → N+1</t>
+          <t>Tamil renders in Noto Serif Tamil, English in Inter. No ???. Bullets render as bullets.</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
@@ -5207,23 +5204,23 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Drawer</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Category filter narrows list</t>
+          <t>PDF iframe + audio playback work</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>1. Pick 'action_required' from Category filter
-2. Verify row set</t>
+          <t>1. Open a drawer with a PDF upload → verify iframe renders (not blocked:other)
+2. Open one with an audio upload → play + seek</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Only action_required rows visible; count pill updates; URL reflects the filter</t>
+          <t>PDF iframe: XFO SAMEORIGIN + frame-ancestors 'self' honoured (CI-89 regression). Audio: Range requests supported, seek works, duration finite on WebM/Opus.</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
@@ -5232,7 +5229,11 @@
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr"/>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>CI-89 iframe fix regression, PERF-audio Range</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="60" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -5247,23 +5248,24 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Priority filter narrows list</t>
+          <t>Approve → Ticket created, status flips REVIEWED</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>1. Pick 'high' priority
-2. Verify</t>
+          <t>1. Open a drawer
+2. Click Approve
+3. Verify tickets table + appointment row</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Only high-priority rows visible; empty-state if none</t>
+          <t>New Ticket with correct ticket_number (TKN&lt;year&gt;&lt;ord&gt;), status=OPEN, appointment_id linked. Appt.status → REVIEWED. Row leaves the AWAITING_REVIEW list.</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -5287,23 +5289,24 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Ministry filter narrows list</t>
+          <t>Approve triggers SMS + activity log</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>1. Pick a ministry
-2. Verify row set</t>
+          <t>1. Approve a drawer
+2. Tail Railway logs
+3. Open the resulting ticket's activity</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Only rows for that ministry (from GrievanceSummaryRecord); rows without a GSR are excluded cleanly</t>
+          <t>spawn_bg(_notify) log line present. Activity row: action_type='created', user='pa_admin', payload has {token, appointment_id}.</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
@@ -5327,23 +5330,23 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Submission date range filter</t>
+          <t>Approve is idempotent (double-click safe)</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>1. Set date_from = today, date_to = today
-2. Verify</t>
+          <t>1. Rapidly click Approve twice
+2. Check tickets table</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Only appointments submitted today (IST) shown</t>
+          <t>One ticket only. Button disabled during in-flight submit. No 500.</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -5367,23 +5370,25 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Triage</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Appointment (meeting) date filter</t>
+          <t>Dismiss + Restore round-trip</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>1. Set appt_date_from / appt_date_to to tomorrow
-2. Verify</t>
+          <t>1. Dismiss with reason 'duplicate submission'
+2. Verify row leaves default list
+3. Open DISMISSED filter → Restore
+4. Row returns to AWAITING_REVIEW</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Only appointments with a scheduled slot tomorrow — filters on MLADailyAvailability.date, not created_at</t>
+          <t>Status transitions cleanly both ways. Activity log records dismiss (with reason) + restore.</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
@@ -5407,23 +5412,23 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Edits</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Venue filter (exact match on VenueRegistry.key)</t>
+          <t>Edit citizen name / category / priority / ministry persists</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>1. Pick a venue
-2. Verify</t>
+          <t>1. Change each field via the edit pencil; save; refresh drawer
+2. Verify filters reflect the change immediately (category / ministry / priority)</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Only rows whose Appointment.venue_id equals that key; historical rows for deactivated venues still match by key</t>
+          <t>PATCH /details persists. Name update rehashes the blind-index. AI-inferred values overridden on save. No silent 500 on two-tab conflict — either overwrites cleanly or shows a 'refresh' message.</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
@@ -5447,23 +5452,24 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Attachments</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Search by citizen name (substring)</t>
+          <t>PA adds attachment + caps honoured</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>1. Type a citizen's name in search
-2. Verify</t>
+          <t>1. Add a small PDF from the drawer → CITIZEN UPLOADS count +1
+2. Try 6MB file → expect reject
+3. At 10 attachments → try one more → expect reject</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Rows whose decrypted citizen name contains the substring (case-insensitive)</t>
+          <t>Uploads succeed and preview inline. 5MB size cap + 10-file total cap enforced with a clean human message.</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
@@ -5487,23 +5493,23 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Attachments</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Search by mobile (last-4 or full number)</t>
+          <t>Filename XSS still safe from the drawer path (CITZ-02 regression)</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>1. Search '3210' (last 4 of citizen mobile)
-2. Search full 10-digit mobile</t>
+          <t>1. Upload a PDF renamed to '&lt;script&gt;alert(1)&lt;/script&gt;.pdf' via the PA drawer
+2. Inspect the chip + file preview title</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Both find the citizen. Uses blind-index for full mobile; last-N substring against masked format for last-4.</t>
+          <t>Filename escaped everywhere. No alert dialog. No console error.</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
@@ -5512,7 +5518,11 @@
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr"/>
-      <c r="I108" s="5" t="inlineStr"/>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>CITZ-02 regression via drawer surface</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="60" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
@@ -5527,23 +5537,23 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Signatory dedup</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Search by token number</t>
+          <t>/similar returns candidates, Approve-with-signatories merges</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>1. Search 'TKN2026...' or bare digits
-2. Verify</t>
+          <t>1. Open drawer → GET /api/appointments/{id}/similar
+2. Approve-with-signatories → target an existing ticket</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Row with that token appears at top; other rows filtered out</t>
+          <t>Similar list is category+district-blocked and similarity-scored. Merge attaches current appt as signatory of target; no new Ticket row.</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
@@ -5567,23 +5577,24 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Filters</t>
+          <t>Signatory dedup</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Clear-all filters resets to default</t>
+          <t>Merge preserves BOTH appointments (CI-61 regression)</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>1. Apply 3+ filters
-2. Click Reset / Clear all</t>
+          <t>1. Reproduce CI-61 setup: same doc, two phones, both AWAITING_REVIEW
+2. Approve the first, then Approve-with-signatories the second into the first's ticket
+3. Verify both appointments still linked</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>All filters removed; list returns to full AWAITING_REVIEW view; URL cleaned</t>
+          <t>Neither appointment disappears. The reported bug 'appointment gone after convert' stays fixed via the merge path too.</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
@@ -5592,7 +5603,11 @@
         </is>
       </c>
       <c r="H110" s="5" t="inlineStr"/>
-      <c r="I110" s="5" t="inlineStr"/>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>PRIMARY dedup regression check</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="60" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
@@ -5607,23 +5622,23 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Sort &amp; pagination</t>
+          <t>Signatory dedup</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Default sort (newest submissions first)</t>
+          <t>Concurrent merge — FOR UPDATE lock prevents dup</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>1. Load /ai-review (no sort override)
-2. Compare row order to created_at DESC</t>
+          <t>1. Two browsers open the same drawer
+2. Both click Approve-with-signatories on the same target within 1s</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Newest at top; deterministic tie-break by id (PERF-08 fix)</t>
+          <t>One wins. The other gets a clean 'already merged' message. No duplicate signatory row. No partial state.</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
@@ -5634,7 +5649,7 @@
       <c r="H111" s="5" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Verifies PERF-08 id tie-break on paginated ORDER BY</t>
+          <t>CORR-06 FOR UPDATE lock</t>
         </is>
       </c>
     </row>
@@ -5651,23 +5666,23 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Sort &amp; pagination</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Sort by urgency (CRITICAL &gt; HIGH &gt; MEDIUM &gt; LOW)</t>
+          <t>Comment adds (English + Tamil)</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>1. Choose urgency sort
-2. Verify order</t>
+          <t>1. POST /comment with an English string → reload activity
+2. Post a Tamil comment 'மீண்டும் அழைக்கவும்' → reload</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL rows first, then HIGH, MEDIUM, LOW. Ties broken by created_at DESC + id.</t>
+          <t>Both persist. Both render correctly in the activity feed (no ???, no codec err — the comment path is DB-only, not Gemini).</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
@@ -5691,24 +5706,23 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Sort &amp; pagination</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Pagination — page 2 loads next set</t>
+          <t>Error toasts polished across the review surface</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>1. Seed &gt;25 AWAITING_REVIEW rows
-2. Load /ai-review; verify page 1
-3. Go to page 2</t>
+          <t>1. Trigger 4 failures: 5MB+ attachment, network offline mid-approve, backend 500, invalid edit
+2. Screenshot each toast</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Page 2 has correct next-25; no duplicates; count / total consistent with counts endpoint</t>
+          <t>Every message is user-friendly. Zero tracebacks / 'gemini-2.5-flash' / raw HTTP codes. Routed through businessMessage() (errors.ts).</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
@@ -5732,23 +5746,23 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Drawer content</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Drawer opens on row click; URL updates with token</t>
+          <t>Mobile viewport (375px) — drawer usable</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>1. Click any row
-2. Verify drawer + URL</t>
+          <t>1. Resize to 375x812
+2. Open a drawer; try Approve + Edit + Add attachment</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Drawer slides in; URL updates with ?ticket=&lt;id&gt; or similar; browser back closes it</t>
+          <t>Drawer scales / becomes a full-screen sheet. All actions reachable. No horizontal body scroll.</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
@@ -5759,1641 +5773,8 @@
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr"/>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>PR-23</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>Deep-link to a specific ticket opens the drawer</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>1. Open /ai-review?ticket=&lt;id&gt; directly in a fresh tab</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Page loads with drawer already open on the specified row</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr"/>
-      <c r="I115" s="5" t="inlineStr"/>
-    </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>PR-24</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>Citizen name / mobile (masked) / constituency / district all shown</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer
-2. Scan the OVERVIEW panel</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>All four fields present. Mobile shown as ******3210 (mask), not raw. Constituency / district reflect what was extracted / entered.</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr"/>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>Verifies mask_mobile helper — must never show raw mobile in drawer</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>PR-25</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>Category / priority / ministry badges render with correct colours</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer
-2. Screenshot the badge row</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Category pill, priority pill (colour-coded LOW/MEDIUM/HIGH/CRITICAL), ministry pill. Values match GrievanceSummaryRecord.</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr"/>
-      <c r="I117" s="5" t="inlineStr"/>
-    </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>PR-26</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>AI summary text renders (English + Tamil, no mojibake)</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer where GrievanceSummaryRecord.summary_ta is populated
-2. Toggle language
-3. Verify Tamil renders in Noto Serif Tamil, English in Inter</t>
-        </is>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>Bilingual summary. No ??? or garbled bytes. Bullets render as bullets.</t>
-        </is>
-      </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr"/>
-    </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>PR-27</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>Key details bullets render</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer with key_details populated
-2. Scan the section</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Bullet list of concrete evidence (dates, amounts, section citations, prior escalation)</t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr"/>
-      <c r="I119" s="5" t="inlineStr"/>
-    </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>PR-28</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>Citizen uploads section count matches attachments</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer
-2. Compare the 'CITIZEN UPLOADS N' chip to actual attachment count</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>N equals AppointmentAttachment row count; DOC / IMG / AUDIO badges reflect actual mime types</t>
-        </is>
-      </c>
-      <c r="G120" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr"/>
-    </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>PR-29</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>PDF renders inline in iframe (regression for CI-89)</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer for a ticket with a PDF upload
-2. Verify the PDF renders inside the preview</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Not 'blocked:other'. XFO SAMEORIGIN + frame-ancestors 'self' honoured. Same behaviour as CI-89 but exercised from Petition Review, not Tickets.</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>Regression for iframe preview fix (commit 38a64bc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>PR-30</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>Audio playback works (native &lt;audio&gt; controls + seek)</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer for a ticket with a voice recording
-2. Play the audio; drag the seek bar</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>Native &lt;audio&gt; renders duration correctly (Range requests supported); seek jumps to arbitrary position; no infinite duration on WebM/Opus</t>
-        </is>
-      </c>
-      <c r="G122" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>Verifies Range request handling in serve_stored_file</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>PR-31</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>Drawer content</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>Drawer closes via X button + Esc key</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>1. Open drawer
-2. Press Escape
-3. Reopen; click the X</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>Both close the drawer; URL cleaned; row loses selected state</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr"/>
-      <c r="I123" s="5" t="inlineStr"/>
-    </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>PR-32</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Approve</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>Approve creates a Ticket row</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer
-2. Click Approve
-3. Verify DB / Tickets tab</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>New row in tickets table; ticket.appointment_id = appt.id; ticket.status = OPEN</t>
-        </is>
-      </c>
-      <c r="G124" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr"/>
-      <c r="I124" s="5" t="inlineStr"/>
-    </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>PR-33</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Approve</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>Ticket number generated correctly (year-count)</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>1. Approve N appointments in a row
-2. Check ticket_number pattern</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>TKN&lt;year&gt;&lt;ordinal&gt; format (e.g. TKN2026082300007). Monotonically increasing within the year; no gaps from failed inserts.</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr"/>
-      <c r="I125" s="5" t="inlineStr"/>
-    </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>PR-34</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Approve</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>Appointment.status flips to REVIEWED</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>1. Approve a drawer
-2. Refetch the appointment</t>
-        </is>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>appt.status = 'REVIEWED'; visible in /appointments 'Reviewed' filter</t>
-        </is>
-      </c>
-      <c r="G126" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr"/>
-    </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>PR-35</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Approve</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>Drawer transitions to a 'Ticket created' success state</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>1. Approve
-2. Watch the drawer</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>Approve button becomes success chip / link to new ticket. Row disappears from AWAITING_REVIEW list (either optimistically or after refresh).</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="5" t="inlineStr"/>
-    </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>PR-36</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Approve</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>SMS notification triggered on approve (visible in logs)</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>1. Approve a drawer with a citizen mobile
-2. Tail Railway logs for the SMS dispatch line</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>spawn_bg(_notify(kind='convert_to_petition', ...)) fires; log line 'SMS dispatched' or MSG91 stub log (no real send in test env)</t>
-        </is>
-      </c>
-      <c r="G128" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr"/>
-    </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>PR-37</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Approve</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>Activity log records 'created' event with actor + payload</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>1. Approve a drawer
-2. Open the activity log on the resulting ticket</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>Activity row: action_type='created', user='pa_admin', message references the token, payload has {token, appointment_id}</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr"/>
-    </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>PR-38</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Approve</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>Approve is idempotent — double-click doesn't create two tickets</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>1. Rapidly click Approve twice
-2. Check tickets table</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>One ticket only. Button disabled during in-flight submit. No 500. No orphan appointment status.</t>
-        </is>
-      </c>
-      <c r="G130" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="inlineStr"/>
-    </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>PR-39</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Dismiss</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>Dismiss requires a reason (or explicit confirmation)</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer
-2. Click Dismiss without a reason</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>Prompted for a reason OR confirmation modal. Cancel returns to drawer without change.</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr"/>
-      <c r="I131" s="5" t="inlineStr"/>
-    </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>PR-40</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Dismiss</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>Dismissed appointment removed from default list, added to DISMISSED bucket</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>1. Dismiss a row
-2. Verify default list + DISMISSED filter</t>
-        </is>
-      </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>Row leaves the default (AWAITING_REVIEW) view; visible under a DISMISSED filter / status; appt.status = 'DISMISSED'</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H132" s="5" t="inlineStr"/>
-      <c r="I132" s="5" t="inlineStr"/>
-    </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>PR-41</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Dismiss</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>Restore endpoint sends back to AWAITING_REVIEW</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a DISMISSED row
-2. Click Restore</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>appt.status → 'AWAITING_REVIEW'; row reappears in default list; activity log records 'restored'</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr">
-        <is>
-          <t>Verifies /api/appointments/{id}/restore endpoint</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>PR-42</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>Triage — Dismiss</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr">
-        <is>
-          <t>Activity log records dismiss + reason</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>1. Dismiss with reason 'duplicate submission'
-2. Open activity log</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>Activity row with action_type='dismissed', reason preserved in payload</t>
-        </is>
-      </c>
-      <c r="G134" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr"/>
-      <c r="I134" s="5" t="inlineStr"/>
-    </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>PR-43</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>Manual edits</t>
-        </is>
-      </c>
-      <c r="D135" s="5" t="inlineStr">
-        <is>
-          <t>Edit citizen name (PATCH /details) persists</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>1. Click edit pencil on citizen name
-2. Change name; save
-3. Refresh drawer</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>Name updated on citizen row (encrypted + blind-index rehashed). Drawer shows the new value.</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr"/>
-      <c r="I135" s="5" t="inlineStr"/>
-    </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>PR-44</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>Manual edits</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Edit constituency persists</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>1. Edit constituency; save
-2. Refresh drawer</t>
-        </is>
-      </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>New value persisted on Appointment row</t>
-        </is>
-      </c>
-      <c r="G136" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr"/>
-    </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>PR-45</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>Manual edits</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>Edit category persists + reflects in filter immediately</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>1. Change category from 'other' to 'action_required'
-2. Apply category=action_required filter</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>Row now included in the filtered list; category badge updated in the drawer</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr"/>
-      <c r="I137" s="5" t="inlineStr"/>
-    </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>PR-46</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="inlineStr">
-        <is>
-          <t>Manual edits</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>Edit priority overrides AI-inferred value</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>1. AI set priority=MEDIUM; PA changes to HIGH
-2. Save; refresh</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>GrievanceSummaryRecord (or appt override field) shows HIGH; badge colour updated; sort-by-urgency respects the override</t>
-        </is>
-      </c>
-      <c r="G138" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-    </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>PR-47</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>Manual edits</t>
-        </is>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>Edit ministry persists + reflects in ministry filter</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>1. Change ministry to a different one; save
-2. Apply filter for the new ministry</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>Row appears in the new bucket, disappears from the old</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr"/>
-      <c r="I139" s="5" t="inlineStr"/>
-    </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>PR-48</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>Manual edits</t>
-        </is>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>Edit conflict — two tabs — last-write-wins with clean UI</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>1. Open the same drawer in two tabs
-2. Edit + save in Tab A
-3. Edit + save in Tab B (without refreshing)</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>Second save either succeeds (overwrites) with a clear indicator, OR is rejected with a polite 'this ticket was updated elsewhere — refresh' message. No silent 500 / no lost data.</t>
-        </is>
-      </c>
-      <c r="G140" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr"/>
-    </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>PR-49</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>Attachments</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>PA adds an attachment from drawer — uploads OK + count increments</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer
-2. Use the Add attachment control; upload a small PDF</t>
-        </is>
-      </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>POST /api/appointments/{id}/attachment succeeds; CITIZEN UPLOADS count +1; new chip visible; file preview works</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr"/>
-    </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>PR-50</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>Attachments</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>Attachment respects 5MB size cap + 10-file total cap</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>1. Try uploading a 6MB file → expect reject
-2. When appt already has 10 attachments → try one more → expect reject</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>Clean 413 or client-side block with human message; server-side cap honoured; count never exceeds 10</t>
-        </is>
-      </c>
-      <c r="G142" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr"/>
-      <c r="I142" s="5" t="inlineStr"/>
-    </row>
-    <row r="143" ht="60" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>PR-51</t>
-        </is>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>Attachments</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>Filename XSS (regression for CITZ-02) in Petition Review drawer</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>1. Upload a PDF renamed to '&lt;script&gt;alert(1)&lt;/script&gt;.pdf' via PA drawer
-2. Inspect chip render</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>Filename escaped in drawer chip AND in file preview title. No alert dialog. No console error.</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr"/>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>CITZ-02 regression from the drawer surface</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="60" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>PR-52</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>Signatory dedup</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>Similar-cases endpoint returns close matches</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer
-2. GET /api/appointments/{id}/similar</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>Returns candidate AWAITING_REVIEW rows blocked by category + district, scored by normalized similarity</t>
-        </is>
-      </c>
-      <c r="G144" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr"/>
-      <c r="I144" s="5" t="inlineStr">
-        <is>
-          <t>Verifies /similar endpoint added for merge suggestions</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="60" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>PR-53</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>Signatory dedup</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
-        <is>
-          <t>Approve-with-signatories merges into an existing petition</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>1. Open a drawer with a similar case
-2. Approve-with-signatories → target an existing ticket</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>Current appt merged as a signatory of the target ticket. No new Ticket row. Both citizens visible on the merged ticket's signatory list.</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr"/>
-      <c r="I145" s="5" t="inlineStr"/>
-    </row>
-    <row r="146" ht="60" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>PR-54</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>Signatory dedup</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
-        <is>
-          <t>Merge preserves original citizen's appointment (Phase 1 CI-61 regression)</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>1. Follow the CI-61 scenario end-to-end via the merge flow
-2. Verify both appointments after merge</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>Both citizens' appointments remain linked. Neither disappears. USER-REPORTED bug from Phase 1 stays fixed via the Petition Review path too.</t>
-        </is>
-      </c>
-      <c r="G146" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr"/>
-      <c r="I146" s="5" t="inlineStr"/>
-    </row>
-    <row r="147" ht="60" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>PR-55</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>Signatory dedup</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
-        <is>
-          <t>Concurrent merge (two PAs) — FOR UPDATE lock prevents ghost rows</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>1. Two PAs open the same drawer
-2. Both click Approve-with-signatories on the same target within 1s</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>One wins; the other gets a clean 'already merged / target updated' message. No duplicate signatory row. No partial state.</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr"/>
-      <c r="I147" s="5" t="inlineStr">
-        <is>
-          <t>Verifies CORR-06 FOR UPDATE row-lock on signatory merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>PR-56</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>Signatory dedup</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
-        <is>
-          <t>Cross-department merge respects RBAC gate</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>1. As pa_admin scoped to Dept A, try to merge into a target that lives in Dept B
-2. Verify behavior</t>
-        </is>
-      </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>Either allowed with a warning, OR blocked with a clean 'target belongs to another department' message. Never a silent cross-department mutation.</t>
-        </is>
-      </c>
-      <c r="G148" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr"/>
-      <c r="I148" s="5" t="inlineStr"/>
-    </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>PR-57</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>PA can add a comment via drawer — persists + shows in activity log</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>1. Add a comment via /api/appointments/{id}/comment
-2. Reload the drawer / activity log</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>Comment stored; visible in the activity feed with author + timestamp</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr"/>
-      <c r="I149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150" ht="60" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>PR-58</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
-        <is>
-          <t>Comment supports Tamil characters (no ??? or codec error)</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>1. Add a Tamil comment: 'மீண்டும் அழைக்கவும்'
-2. Reload</t>
-        </is>
-      </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>Tamil preserved end-to-end. No mojibake. No SDK ascii-in-header error (comment path is DB only, not Gemini — so no expected failure).</t>
-        </is>
-      </c>
-      <c r="G150" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H150" s="5" t="inlineStr"/>
-      <c r="I150" s="5" t="inlineStr"/>
-    </row>
-    <row r="151" ht="60" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>PR-59</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>Cross-cutting UX</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>All error toasts polished across Petition Review</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>1. Trigger errors: 5MB+ attachment, network offline mid-approve, backend 500, invalid edit
-2. Screenshot each toast</t>
-        </is>
-      </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>Zero tracebacks. Zero 'gemini-2.5-flash'. Zero raw HTTP codes. All messages routed through businessMessage() (frontend errors.ts).</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr"/>
-      <c r="I151" s="5" t="inlineStr"/>
-    </row>
-    <row r="152" ht="60" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
-        <is>
-          <t>PR-60</t>
-        </is>
-      </c>
-      <c r="B152" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>Cross-cutting UX</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="inlineStr">
-        <is>
-          <t>Loading skeleton on drawer open (&gt;200ms fetch)</t>
-        </is>
-      </c>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>1. Throttle network to 'Slow 3G' in devtools
-2. Open a drawer</t>
-        </is>
-      </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>Skeleton / spinner visible while fetching. No content flash. No blank white area.</t>
-        </is>
-      </c>
-      <c r="G152" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr"/>
-      <c r="I152" s="5" t="inlineStr"/>
-    </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>PR-61</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>Cross-cutting UX</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
-        <is>
-          <t>Mobile viewport (375px) — drawer usable, no horizontal scroll</t>
-        </is>
-      </c>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>1. Resize to 375x812
-2. Open a drawer</t>
-        </is>
-      </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>Drawer either becomes a full-screen sheet or scales down. All actions reachable with thumbs. No horizontal scroll on body.</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
-      <c r="I153" s="5" t="inlineStr"/>
-    </row>
-    <row r="154" ht="60" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>PR-62</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>Cross-cutting UX</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
-        <is>
-          <t>Polling refresh — new petitions appear without full page reload</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>1. Load /ai-review; note current count
-2. In another tab / device, submit a new petition
-3. Wait for the polling interval</t>
-        </is>
-      </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>New row appears in the list; count updates. No full-page refresh needed. Drawer content preserved if open on a different row.</t>
-        </is>
-      </c>
-      <c r="G154" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H154" s="5" t="inlineStr"/>
-      <c r="I154" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I154"/>
+  <autoFilter ref="A1:I114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,12 +53,8 @@
       <b val="1"/>
       <color rgb="005B21B6"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00374151"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,11 +74,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDE9FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,9 +118,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,7 +531,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4a26213</t>
+          <t>3f0df68</t>
         </is>
       </c>
     </row>
@@ -595,7 +583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +603,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -655,7 +643,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +654,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3371,16 @@
           <t>Two independent tickets, both AWAITING_REVIEW; both appointments visible</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
           <t>Setup for CI-60/61. Awaiting focused end-to-end pass — reported-bug regression.</t>
@@ -3427,12 +3419,16 @@
           <t>Petition row created; A's appointment still linked; ticket advances</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="60" customHeight="1">
@@ -3467,12 +3463,16 @@
           <t>Either merges into A's signatory list WITH B's appointment PRESERVED, OR creates B as separate petition. B's appointment must not vanish.</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
           <t>USER-REPORTED BUG: 'appointment gone and not found in the petition too'. Focus of the dedup pass.</t>
@@ -3511,12 +3511,16 @@
           <t>Second recognized as same citizen (mobile blind index match); either updates name or flags conflict; no duplicate citizen row</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>Verifies Fernet encryption + SHA-256 blind index</t>
@@ -3555,12 +3559,16 @@
           <t>Recognized as same citizen; name normalization consistent</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="60" customHeight="1">
@@ -3595,12 +3603,16 @@
           <t>Both persisted OR one wins with clean dedup; no orphan rows, no partial state, no double-commit</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>Verifies CORR-06 signatory merge FOR UPDATE row-lock</t>
@@ -4896,12 +4908,16 @@
           <t>pa_admin sees the list. dept_officer redirected to /tickets (per _no_dept_officer gate).</t>
         </is>
       </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I93" s="5" t="inlineStr"/>
     </row>
     <row r="94" ht="60" customHeight="1">
@@ -4936,12 +4952,16 @@
           <t>302 to /auth/login; no traceback; no data leaked</t>
         </is>
       </c>
-      <c r="G94" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="60" customHeight="1">
@@ -4976,12 +4996,16 @@
           <t>Only AWAITING_REVIEW rows appear. Empty-state is friendly when count is zero.</t>
         </is>
       </c>
-      <c r="G95" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I95" s="5" t="inlineStr"/>
     </row>
     <row r="96" ht="60" customHeight="1">
@@ -5017,12 +5041,16 @@
           <t>Each control narrows the list correctly. Newest-first default has an id tie-break (PERF-08). Clear-all restores.</t>
         </is>
       </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr"/>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="60" customHeight="1">
@@ -5058,12 +5086,16 @@
           <t>Page 2 shows next 25 (no dupes). Counts match exactly (no IST/UTC drift). Fresh submission appears after the polling interval.</t>
         </is>
       </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="inlineStr"/>
     </row>
     <row r="98" ht="60" customHeight="1">
@@ -5099,12 +5131,16 @@
           <t>Both entry points open the drawer with the right row. X and Esc close it. Browser back closes it too.</t>
         </is>
       </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr"/>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="60" customHeight="1">
@@ -5139,12 +5175,16 @@
           <t>Name / masked mobile (******3210) / constituency / district present. Category + priority (colour-coded) + ministry pills reflect GSR.</t>
         </is>
       </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
           <t>Mobile mask regression</t>
@@ -5183,12 +5223,16 @@
           <t>Tamil renders in Noto Serif Tamil, English in Inter. No ???. Bullets render as bullets.</t>
         </is>
       </c>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr"/>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="60" customHeight="1">
@@ -5223,12 +5267,16 @@
           <t>PDF iframe: XFO SAMEORIGIN + frame-ancestors 'self' honoured (CI-89 regression). Audio: Range requests supported, seek works, duration finite on WebM/Opus.</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr"/>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
           <t>CI-89 iframe fix regression, PERF-audio Range</t>
@@ -5268,12 +5316,16 @@
           <t>New Ticket with correct ticket_number (TKN&lt;year&gt;&lt;ord&gt;), status=OPEN, appointment_id linked. Appt.status → REVIEWED. Row leaves the AWAITING_REVIEW list.</t>
         </is>
       </c>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="60" customHeight="1">
@@ -5309,12 +5361,16 @@
           <t>spawn_bg(_notify) log line present. Activity row: action_type='created', user='pa_admin', payload has {token, appointment_id}.</t>
         </is>
       </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr"/>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I103" s="5" t="inlineStr"/>
     </row>
     <row r="104" ht="60" customHeight="1">
@@ -5349,12 +5405,16 @@
           <t>One ticket only. Button disabled during in-flight submit. No 500.</t>
         </is>
       </c>
-      <c r="G104" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H104" s="5" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I104" s="5" t="inlineStr"/>
     </row>
     <row r="105" ht="60" customHeight="1">
@@ -5391,12 +5451,16 @@
           <t>Status transitions cleanly both ways. Activity log records dismiss (with reason) + restore.</t>
         </is>
       </c>
-      <c r="G105" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I105" s="5" t="inlineStr"/>
     </row>
     <row r="106" ht="60" customHeight="1">
@@ -5431,12 +5495,16 @@
           <t>PATCH /details persists. Name update rehashes the blind-index. AI-inferred values overridden on save. No silent 500 on two-tab conflict — either overwrites cleanly or shows a 'refresh' message.</t>
         </is>
       </c>
-      <c r="G106" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H106" s="5" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I106" s="5" t="inlineStr"/>
     </row>
     <row r="107" ht="60" customHeight="1">
@@ -5472,12 +5540,16 @@
           <t>Uploads succeed and preview inline. 5MB size cap + 10-file total cap enforced with a clean human message.</t>
         </is>
       </c>
-      <c r="G107" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I107" s="5" t="inlineStr"/>
     </row>
     <row r="108" ht="60" customHeight="1">
@@ -5512,12 +5584,16 @@
           <t>Filename escaped everywhere. No alert dialog. No console error.</t>
         </is>
       </c>
-      <c r="G108" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
           <t>CITZ-02 regression via drawer surface</t>
@@ -5556,12 +5632,16 @@
           <t>Similar list is category+district-blocked and similarity-scored. Merge attaches current appt as signatory of target; no new Ticket row.</t>
         </is>
       </c>
-      <c r="G109" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr"/>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I109" s="5" t="inlineStr"/>
     </row>
     <row r="110" ht="60" customHeight="1">
@@ -5597,12 +5677,16 @@
           <t>Neither appointment disappears. The reported bug 'appointment gone after convert' stays fixed via the merge path too.</t>
         </is>
       </c>
-      <c r="G110" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H110" s="5" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
           <t>PRIMARY dedup regression check</t>
@@ -5641,12 +5725,16 @@
           <t>One wins. The other gets a clean 'already merged' message. No duplicate signatory row. No partial state.</t>
         </is>
       </c>
-      <c r="G111" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr"/>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
           <t>CORR-06 FOR UPDATE lock</t>
@@ -5685,12 +5773,16 @@
           <t>Both persist. Both render correctly in the activity feed (no ???, no codec err — the comment path is DB-only, not Gemini).</t>
         </is>
       </c>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H112" s="5" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I112" s="5" t="inlineStr"/>
     </row>
     <row r="113" ht="60" customHeight="1">
@@ -5725,12 +5817,16 @@
           <t>Every message is user-friendly. Zero tracebacks / 'gemini-2.5-flash' / raw HTTP codes. Routed through businessMessage() (errors.ts).</t>
         </is>
       </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr"/>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I113" s="5" t="inlineStr"/>
     </row>
     <row r="114" ht="60" customHeight="1">
@@ -5765,12 +5861,16 @@
           <t>Drawer scales / becomes a full-screen sheet. All actions reachable. No horizontal body scroll.</t>
         </is>
       </c>
-      <c r="G114" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H114" s="5" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I114" s="5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,12 @@
       <b val="1"/>
       <color rgb="005B21B6"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00374151"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +127,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -555,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P2 — PA Petition Review</t>
+          <t>P3 — Tickets / Association Review</t>
         </is>
       </c>
     </row>
@@ -573,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -654,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -672,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5873,8 +5885,837 @@
       </c>
       <c r="I114" s="5" t="inlineStr"/>
     </row>
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>TK-01</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Access</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>RBAC — pa_admin sees all, dept_officer sees only their dept</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as pa_admin → /tickets
+2. Log in as dept_officer → /tickets</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>pa_admin: full ticket list across every dept. dept_officer: only tickets routed to their department; other rows never surface.</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr"/>
+      <c r="I115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>TK-02</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — List</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Status tabs partition correctly (Open / Assigned / Forwarded / Resolved / Closed)</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>1. Click each status tab in turn
+2. Verify row set + counts</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Each tab shows only its status. Rows never appear on the wrong tab. Terminal tabs (Resolved/Closed) don't show OPEN or FORWARDED rows.</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr"/>
+      <c r="I116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>TK-03</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — List</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Filter + search + sort — pill counts follow the current filter (3f0df68 regression)</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>1. Apply priority=high → verify Open pill narrows with list
+2. Search by ticket number / citizen name → verify
+3. Sort by created / due-date / priority → verify order</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Pill counts = visible list count for the same tab (no stable-universe mismatch). SLA-breached chip also narrows with the filter (already WYSIWYG per 0cde4ed).</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr"/>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Regression for 3f0df68 pill-count parity (aligns tickets with appointments + ai-review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>TK-04</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Drawer</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Drawer overview: badges + source-specific detail block</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a citizen-petition ticket → verify priority/dept/status badges + AI summary
+2. Open an association-minted ticket → verify AssociationDetail block appears (rep name, ministry, docs)</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Citizen tickets show petition summary + key details. Association tickets additionally show source_kind='association' detail card (a4bacc9).</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr"/>
+      <c r="I118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>TK-05</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Triage</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Assign requires only dept (no due-date coupling) — 2d1ee54 regression</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>1. Open an OPEN ticket with no due-date set
+2. Pick a dept, DON'T touch due-date
+3. Click Assign</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Assign button enables as soon as a dept is picked. Save routes to dept + logs 'routed'. Previous bug: button stayed disabled without a due-date.</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr"/>
+      <c r="I119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>TK-06</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Triage</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Due-date + priority live-save on non-OPEN tickets (decc4f4 regression)</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>1. Open an association-auto-forwarded ticket (status=FORWARDED_TO_DEPT)
+2. Change priority
+3. Pick a due-date</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Both fields save immediately (canEditSla path). Prior bug: everything was disabled because canEdit gated on status===open.</t>
+        </is>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr"/>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Also implicitly verifies AR-06 auto-forward chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>TK-07</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Lifecycle</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Dept accept → assign locks; Resolve → Reopen round-trip</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>1. As dept_officer, accept a forwarded ticket → accepted_at set
+2. Verify PA drawer shows accepted chip, assign dropdown gone
+3. Dept resolves → status=RESOLVED
+4. PA reopens → status=REOPENED</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>accepted_at persists. Status transitions cleanly both ways. Activity log records accept / resolve / reopen with actor + payload.</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr"/>
+      <c r="I121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>TK-08</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Attachments</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Attachment upload from drawer + filename XSS safe</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>1. Upload a small PDF via ticket drawer → count +1
+2. Upload '&lt;script&gt;alert(1)&lt;/script&gt;.pdf' → escaped in chip + preview title</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Upload succeeds. Filename rendered as text everywhere. 5MB cap honoured.</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr"/>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>CITZ-02 regression on ticket surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>TK-09</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Attachments</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Dept can view ai_uploads/ PDFs for their tickets (cbc9c8c regression)</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as dept_officer, open a ticket derived from an AI upload
+2. Click the citizen's original PDF
+3. Verify iframe renders</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>PDF renders inline (200 OK). Cross-dept access still 403. Prior bug: /department/api/files/ai_uploads/… → 403 for legitimate access.</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr"/>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Regression for cbc9c8c (ai_uploads/ branch in _dept_authorize_file) + f40c2f6 (HTTPException import — 500→403 for legit denies)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>TK-10</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Comments</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>PA + dept can comment; Tamil supported</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>1. PA adds English comment → visible in activity
+2. Dept adds Tamil comment 'மீண்டும் அழைக்கவும்' → renders correctly</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Both comments persist with author + timestamp. Tamil no ??? no codec err.</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr"/>
+      <c r="I124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>TK-11</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Tickets — Drawer</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Drawer prev/next navigation (5c3bc5b regression)</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a ticket drawer
+2. Use prev/next arrows (or keyboard)</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Drawer swaps to sibling row without full-page reload. URL updates. Selection state moves.</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr"/>
+      <c r="I125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>AR-01</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Assoc Review — Access</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>RBAC — pa_admin only</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as pa_admin → /association-review
+2. Log in as dept_officer → /association-review</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>pa_admin loads normally. dept_officer redirected or 403 (dept has no association-review UI).</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr"/>
+      <c r="I126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>AR-02</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Assoc Review — List</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Default list + status filter partition</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>1. Load /association-review (default = AWAITING_REVIEW)
+2. Switch tabs — Awaiting / Approved / Rejected</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Each tab shows only its status. Empty-state is friendly. Counts match visible rows.</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr"/>
+      <c r="I127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>AR-03</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Assoc Review — Drawer</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Drawer content — rep, ministry, extraction, uploaded documents</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a submission with 2+ documents
+2. Scan the drawer</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Representative name + phone + org, chosen ministry, AssociationExtraction summary + key details, document previews render inline (iframe).</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr"/>
+      <c r="I128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>AR-04</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Assoc Review — Triage</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Ministry-driven decision — override + approve</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a submission where AI ministry = 'other'
+2. Override to a real ministry via inline edit
+3. Approve → verify Ticket minted</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Ministry edit persists on the row. Approve calls mint_ticket_from_association → Appointment + Ticket + GSR created. Redirect / drawer transitions to 'submitted' state.</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr"/>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Regression for 40a6f55 ministry-driven decision refactor</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>AR-05</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Assoc Review — Triage</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Non-school ministry → auto-forward chain (feeds TK-06)</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve an association with ministry=health_medical_education
+2. Open the resulting Ticket in /tickets</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Ticket exists with status=FORWARDED_TO_DEPT (auto-forwarded via forward_if_non_school). Dept officer can accept from their workspace. SLA fields still editable (see TK-06).</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr"/>
+      <c r="I130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>AR-06</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Assoc Review — Triage</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>School ministry → stays OPEN for PA to assign</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>1. Approve an association with ministry=school_education_tamil_dev_info_publicity
+2. Open the resulting Ticket</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Ticket exists with status=OPEN. Assign panel visible so PA can route to one of the 10 school departments. Contrast with AR-05.</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr"/>
+      <c r="I131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>AR-07</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Assoc Review — Dismiss</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Reject with reason + restore</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>1. Reject a submission with reason 'incomplete documentation'
+2. Verify status=REJECTED
+3. Restore back to AWAITING_REVIEW</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Reason preserved on the row. Restore reverses cleanly. Activity log records both actions.</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr"/>
+      <c r="I132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>T3-01</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Polished error toasts across tickets + association review</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>1. Trigger 4 failures: 5MB+ attachment, network offline mid-approve, backend 500, invalid edit
+2. Screenshot each toast on both surfaces</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Every message user-friendly. Zero tracebacks / raw HTTP codes / 'gemini-2.5-flash'. Routed through businessMessage() (errors.ts).</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr"/>
+      <c r="I133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>T3-02</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Mobile viewport (375px) — both drawers usable</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>1. Resize to 375x812
+2. Open ticket drawer → try Assign / Comment / Add attachment
+3. Open association drawer → try Approve / Ministry override</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Both drawers scale / go full-screen. All actions reachable with thumbs. No horizontal body scroll.</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr"/>
+      <c r="I134" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I114"/>
+  <autoFilter ref="A1:I134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P3 — Tickets / Association Review</t>
+          <t>P4 — Events (voice + photo)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -666,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6714,8 +6714,708 @@
       <c r="H134" s="5" t="inlineStr"/>
       <c r="I134" s="5" t="inlineStr"/>
     </row>
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>EV-01</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Events — Access</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Events login works with seeded events_reviewer credentials</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in to /dashboard/login as admin-office (seeds event_reviewer role)
+2. Then log in to /events/login with the same credentials</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Both logins succeed. events_session cookie set. No 401 / no 'unauthorized' with legitimate creds.</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr"/>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Verifies events_auth.py real-user path (env-credential path was removed — see prior incident)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>EV-02</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Events — Access</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Direct URL without events_session → clean redirect</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>1. Wipe events_session cookie
+2. Navigate to /events directly</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Redirect to /events/login. No 500 / no blank page.</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr"/>
+      <c r="I136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>EV-03</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Events — Add</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Manual event add (title / venue / date / note) → appears in list</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>1. Open events UI, click Add Event
+2. Fill title, venue, date, optional note
+3. Save</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>New row in list. All fields populated. No AI extraction path fired for manual entry.</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>EV-04</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Events — Voice</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Tamil voice add → 200 OK, extraction runs (SDK ASCII fix regression)</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>1. Record a 20s Tamil voice describing an event
+2. Upload via voice add flow</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>200 OK. Extraction populates title_en / title_ta / venue / date. NO UnicodeEncodeError. NO 500 from the google-genai httpx header path.</t>
+        </is>
+      </c>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Regression for event_service.py _ascii_safe fix (voice-note ASCII scrub before Gemini call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>EV-05</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Events — Voice</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Tamil voice + Tamil note field → 200 OK</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>1. Same as EV-04
+2. Type Tamil text into the note field before upload</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>200 OK. Note preserved on the event row. No header-encoding crash.</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>EV-06</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Events — Voice</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>English voice add → extraction runs</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>1. Record 20s English voice describing an event
+2. Upload</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Extraction returns English title / venue. Row created.</t>
+        </is>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>EV-07</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Events — Photo</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Photo add — invitation card image → OCR extraction</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>1. Upload a photo of an invitation card
+2. Wait for extraction</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>title / venue / date extracted; row appears in list with source doc viewable inline.</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>EV-08</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Events — Photo</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Blurry / non-invitation image → polished error (businessMessage)</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>1. Upload a random selfie / blurry image
+2. Watch EventPopup / error toast</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>User-friendly message ('could not read'). NO Python traceback. NO 'gemini-2.5-flash' / 'codec' strings.</t>
+        </is>
+      </c>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr"/>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Regression for TECHNICAL regex + businessMessage() in EventPopup</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>EV-09</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Events — List</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Default list shows upcoming events</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>1. Load /events
+2. Verify default view</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Upcoming events (date &gt;= today) sorted by date ascending. Past events hidden or in a separate section.</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144" ht="60" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>EV-10</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Events — List</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Date range filter + search by title/venue</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>1. Apply a date range → verify rows narrow
+2. Search by partial title / venue name</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Both narrow the visible set correctly. Clear-all restores.</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr"/>
+      <c r="I144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145" ht="60" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>EV-11</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Events — Detail</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>EventPopup opens on row click with bilingual content</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>1. Click a Tamil-added event (has title_ta populated)
+2. Toggle language</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Popup shows title / venue / note in the selected language via title_ta / venue_ta fields. No mojibake.</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr"/>
+      <c r="I145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146" ht="60" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>EV-12</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Events — Detail</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Error field renders polished text (businessMessage regression)</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>1. Force an event to be in the error_message state (upload a bad file OR find a historically-failed event)
+2. Open EventPopup</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>error_message rendered via businessMessage() — user-friendly text, not raw 'UnicodeEncodeError: ascii codec can't encode...' or 'gemini-2.5-flash failed on all models'.</t>
+        </is>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Regression for 5bbbc1c EventPopup businessMessage() wiring + TECHNICAL regex</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="60" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>EV-13</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Events — Edit</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Edit event fields → persists</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>1. Open an existing event
+2. Edit title / venue / date
+3. Save; reload</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Changes persist across reload. Activity log or last-updated stamp reflects the edit.</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr"/>
+      <c r="I147" s="5" t="inlineStr"/>
+    </row>
+    <row r="148" ht="60" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>EV-14</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Events — Edit</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Delete event → gone from list</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>1. Delete an event (with confirmation)
+2. Verify list</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Row removed. No orphan attachments left in storage (soft delete OK if that's the design).</t>
+        </is>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr"/>
+      <c r="I148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>EV-15</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Events — Edit</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Concurrent edit (two tabs) — clean last-write-wins</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>1. Open same event in two tabs
+2. Edit + save in tab A
+3. Edit + save in tab B without refresh</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Second save overwrites cleanly OR clean 'this event was updated elsewhere' message. No silent 500 / no lost data.</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150" ht="60" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>T4-01</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>All error toasts polished across the events surface</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>1. Trigger failures: 5MB+ audio, 5MB+ image, network offline mid-upload, backend 500, invalid extract
+2. Screenshot each toast</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Every message user-friendly. Zero tracebacks / raw HTTP codes / 'gemini-*' / 'codec'. Routed through the businessMessage() polish path.</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr"/>
+      <c r="I150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151" ht="60" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>T4-02</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Mobile viewport (375px) — record voice + view event usable</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>1. Resize to 375x812
+2. Try the voice-add recorder
+3. Open EventPopup</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Recorder buttons reachable. Popup scales / goes full-screen. No horizontal body scroll.</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr"/>
+      <c r="I151" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I134"/>
+  <autoFilter ref="A1:I151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3f0df68</t>
+          <t>daa51f8</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -5917,12 +5917,16 @@
           <t>pa_admin: full ticket list across every dept. dept_officer: only tickets routed to their department; other rows never surface.</t>
         </is>
       </c>
-      <c r="G115" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr"/>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I115" s="5" t="inlineStr"/>
     </row>
     <row r="116" ht="60" customHeight="1">
@@ -5957,12 +5961,16 @@
           <t>Each tab shows only its status. Rows never appear on the wrong tab. Terminal tabs (Resolved/Closed) don't show OPEN or FORWARDED rows.</t>
         </is>
       </c>
-      <c r="G116" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H116" s="5" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I116" s="5" t="inlineStr"/>
     </row>
     <row r="117" ht="60" customHeight="1">
@@ -5998,12 +6006,16 @@
           <t>Pill counts = visible list count for the same tab (no stable-universe mismatch). SLA-breached chip also narrows with the filter (already WYSIWYG per 0cde4ed).</t>
         </is>
       </c>
-      <c r="G117" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr"/>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
           <t>Regression for 3f0df68 pill-count parity (aligns tickets with appointments + ai-review)</t>
@@ -6042,12 +6054,16 @@
           <t>Citizen tickets show petition summary + key details. Association tickets additionally show source_kind='association' detail card (a4bacc9).</t>
         </is>
       </c>
-      <c r="G118" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H118" s="5" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I118" s="5" t="inlineStr"/>
     </row>
     <row r="119" ht="60" customHeight="1">
@@ -6083,12 +6099,16 @@
           <t>Assign button enables as soon as a dept is picked. Save routes to dept + logs 'routed'. Previous bug: button stayed disabled without a due-date.</t>
         </is>
       </c>
-      <c r="G119" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr"/>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I119" s="5" t="inlineStr"/>
     </row>
     <row r="120" ht="60" customHeight="1">
@@ -6124,12 +6144,16 @@
           <t>Both fields save immediately (canEditSla path). Prior bug: everything was disabled because canEdit gated on status===open.</t>
         </is>
       </c>
-      <c r="G120" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr"/>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
           <t>Also implicitly verifies AR-06 auto-forward chain</t>
@@ -6170,12 +6194,16 @@
           <t>accepted_at persists. Status transitions cleanly both ways. Activity log records accept / resolve / reopen with actor + payload.</t>
         </is>
       </c>
-      <c r="G121" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I121" s="5" t="inlineStr"/>
     </row>
     <row r="122" ht="60" customHeight="1">
@@ -6210,12 +6238,16 @@
           <t>Upload succeeds. Filename rendered as text everywhere. 5MB cap honoured.</t>
         </is>
       </c>
-      <c r="G122" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
           <t>CITZ-02 regression on ticket surface</t>
@@ -6255,12 +6287,16 @@
           <t>PDF renders inline (200 OK). Cross-dept access still 403. Prior bug: /department/api/files/ai_uploads/… → 403 for legitimate access.</t>
         </is>
       </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
           <t>Regression for cbc9c8c (ai_uploads/ branch in _dept_authorize_file) + f40c2f6 (HTTPException import — 500→403 for legit denies)</t>
@@ -6299,12 +6335,16 @@
           <t>Both comments persist with author + timestamp. Tamil no ??? no codec err.</t>
         </is>
       </c>
-      <c r="G124" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H124" s="5" t="inlineStr"/>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I124" s="5" t="inlineStr"/>
     </row>
     <row r="125" ht="60" customHeight="1">
@@ -6339,12 +6379,16 @@
           <t>Drawer swaps to sibling row without full-page reload. URL updates. Selection state moves.</t>
         </is>
       </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr"/>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="inlineStr"/>
     </row>
     <row r="126" ht="60" customHeight="1">
@@ -6379,12 +6423,16 @@
           <t>pa_admin loads normally. dept_officer redirected or 403 (dept has no association-review UI).</t>
         </is>
       </c>
-      <c r="G126" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H126" s="5" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I126" s="5" t="inlineStr"/>
     </row>
     <row r="127" ht="60" customHeight="1">
@@ -6419,12 +6467,16 @@
           <t>Each tab shows only its status. Empty-state is friendly. Counts match visible rows.</t>
         </is>
       </c>
-      <c r="G127" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I127" s="5" t="inlineStr"/>
     </row>
     <row r="128" ht="60" customHeight="1">
@@ -6459,12 +6511,16 @@
           <t>Representative name + phone + org, chosen ministry, AssociationExtraction summary + key details, document previews render inline (iframe).</t>
         </is>
       </c>
-      <c r="G128" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I128" s="5" t="inlineStr"/>
     </row>
     <row r="129" ht="60" customHeight="1">
@@ -6500,12 +6556,16 @@
           <t>Ministry edit persists on the row. Approve calls mint_ticket_from_association → Appointment + Ticket + GSR created. Redirect / drawer transitions to 'submitted' state.</t>
         </is>
       </c>
-      <c r="G129" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
           <t>Regression for 40a6f55 ministry-driven decision refactor</t>
@@ -6544,12 +6604,16 @@
           <t>Ticket exists with status=FORWARDED_TO_DEPT (auto-forwarded via forward_if_non_school). Dept officer can accept from their workspace. SLA fields still editable (see TK-06).</t>
         </is>
       </c>
-      <c r="G130" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I130" s="5" t="inlineStr"/>
     </row>
     <row r="131" ht="60" customHeight="1">
@@ -6584,12 +6648,16 @@
           <t>Ticket exists with status=OPEN. Assign panel visible so PA can route to one of the 10 school departments. Contrast with AR-05.</t>
         </is>
       </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr"/>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I131" s="5" t="inlineStr"/>
     </row>
     <row r="132" ht="60" customHeight="1">
@@ -6625,12 +6693,16 @@
           <t>Reason preserved on the row. Restore reverses cleanly. Activity log records both actions.</t>
         </is>
       </c>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H132" s="5" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I132" s="5" t="inlineStr"/>
     </row>
     <row r="133" ht="60" customHeight="1">
@@ -6665,12 +6737,16 @@
           <t>Every message user-friendly. Zero tracebacks / raw HTTP codes / 'gemini-2.5-flash'. Routed through businessMessage() (errors.ts).</t>
         </is>
       </c>
-      <c r="G133" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr"/>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="inlineStr"/>
     </row>
     <row r="134" ht="60" customHeight="1">
@@ -6706,12 +6782,16 @@
           <t>Both drawers scale / go full-screen. All actions reachable with thumbs. No horizontal body scroll.</t>
         </is>
       </c>
-      <c r="G134" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I134" s="5" t="inlineStr"/>
     </row>
     <row r="135" ht="60" customHeight="1">

--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P4 — Events (voice + photo)</t>
+          <t>P5 — Executive / Dept / Minister</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6826,12 +6826,16 @@
           <t>Both logins succeed. events_session cookie set. No 401 / no 'unauthorized' with legitimate creds.</t>
         </is>
       </c>
-      <c r="G135" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
           <t>Verifies events_auth.py real-user path (env-credential path was removed — see prior incident)</t>
@@ -6870,12 +6874,16 @@
           <t>Redirect to /events/login. No 500 / no blank page.</t>
         </is>
       </c>
-      <c r="G136" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I136" s="5" t="inlineStr"/>
     </row>
     <row r="137" ht="60" customHeight="1">
@@ -6911,12 +6919,16 @@
           <t>New row in list. All fields populated. No AI extraction path fired for manual entry.</t>
         </is>
       </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr"/>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I137" s="5" t="inlineStr"/>
     </row>
     <row r="138" ht="60" customHeight="1">
@@ -6951,12 +6963,16 @@
           <t>200 OK. Extraction populates title_en / title_ta / venue / date. NO UnicodeEncodeError. NO 500 from the google-genai httpx header path.</t>
         </is>
       </c>
-      <c r="G138" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H138" s="5" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
           <t>Regression for event_service.py _ascii_safe fix (voice-note ASCII scrub before Gemini call)</t>
@@ -6995,12 +7011,16 @@
           <t>200 OK. Note preserved on the event row. No header-encoding crash.</t>
         </is>
       </c>
-      <c r="G139" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="inlineStr"/>
     </row>
     <row r="140" ht="60" customHeight="1">
@@ -7035,12 +7055,16 @@
           <t>Extraction returns English title / venue. Row created.</t>
         </is>
       </c>
-      <c r="G140" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H140" s="5" t="inlineStr"/>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I140" s="5" t="inlineStr"/>
     </row>
     <row r="141" ht="60" customHeight="1">
@@ -7075,12 +7099,16 @@
           <t>title / venue / date extracted; row appears in list with source doc viewable inline.</t>
         </is>
       </c>
-      <c r="G141" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="inlineStr"/>
     </row>
     <row r="142" ht="60" customHeight="1">
@@ -7115,12 +7143,16 @@
           <t>User-friendly message ('could not read'). NO Python traceback. NO 'gemini-2.5-flash' / 'codec' strings.</t>
         </is>
       </c>
-      <c r="G142" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H142" s="5" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
           <t>Regression for TECHNICAL regex + businessMessage() in EventPopup</t>
@@ -7159,12 +7191,16 @@
           <t>Upcoming events (date &gt;= today) sorted by date ascending. Past events hidden or in a separate section.</t>
         </is>
       </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I143" s="5" t="inlineStr"/>
     </row>
     <row r="144" ht="60" customHeight="1">
@@ -7199,12 +7235,16 @@
           <t>Both narrow the visible set correctly. Clear-all restores.</t>
         </is>
       </c>
-      <c r="G144" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="60" customHeight="1">
@@ -7239,12 +7279,16 @@
           <t>Popup shows title / venue / note in the selected language via title_ta / venue_ta fields. No mojibake.</t>
         </is>
       </c>
-      <c r="G145" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr"/>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I145" s="5" t="inlineStr"/>
     </row>
     <row r="146" ht="60" customHeight="1">
@@ -7279,12 +7323,16 @@
           <t>error_message rendered via businessMessage() — user-friendly text, not raw 'UnicodeEncodeError: ascii codec can't encode...' or 'gemini-2.5-flash failed on all models'.</t>
         </is>
       </c>
-      <c r="G146" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H146" s="5" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
           <t>Regression for 5bbbc1c EventPopup businessMessage() wiring + TECHNICAL regex</t>
@@ -7324,12 +7372,16 @@
           <t>Changes persist across reload. Activity log or last-updated stamp reflects the edit.</t>
         </is>
       </c>
-      <c r="G147" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr"/>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I147" s="5" t="inlineStr"/>
     </row>
     <row r="148" ht="60" customHeight="1">
@@ -7364,12 +7416,16 @@
           <t>Row removed. No orphan attachments left in storage (soft delete OK if that's the design).</t>
         </is>
       </c>
-      <c r="G148" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H148" s="5" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I148" s="5" t="inlineStr"/>
     </row>
     <row r="149" ht="60" customHeight="1">
@@ -7405,12 +7461,16 @@
           <t>Second save overwrites cleanly OR clean 'this event was updated elsewhere' message. No silent 500 / no lost data.</t>
         </is>
       </c>
-      <c r="G149" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr"/>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I149" s="5" t="inlineStr"/>
     </row>
     <row r="150" ht="60" customHeight="1">
@@ -7445,12 +7505,16 @@
           <t>Every message user-friendly. Zero tracebacks / raw HTTP codes / 'gemini-*' / 'codec'. Routed through the businessMessage() polish path.</t>
         </is>
       </c>
-      <c r="G150" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H150" s="5" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I150" s="5" t="inlineStr"/>
     </row>
     <row r="151" ht="60" customHeight="1">
@@ -7486,16 +7550,860 @@
           <t>Recorder buttons reachable. Popup scales / goes full-screen. No horizontal body scroll.</t>
         </is>
       </c>
-      <c r="G151" s="8" t="inlineStr">
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152" ht="60" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>EX-01</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Exec Queue — Access</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>RBAC — office admin sees the queue, dept_officer redirected</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as pa_admin → navigate to Executive Queue
+2. Log in as dept_officer → try Executive Queue directly</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>pa_admin loads. dept_officer redirected to /tickets. No cross-role leak.</t>
+        </is>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H151" s="5" t="inlineStr"/>
-      <c r="I151" s="5" t="inlineStr"/>
+      <c r="H152" s="5" t="inlineStr"/>
+      <c r="I152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153" ht="60" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>EX-02</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Exec Queue — List</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>List + filters + pill counts match current view</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>1. Load queue → verify aggregated tickets across depts
+2. Apply priority / dept / status filters
+3. Check pill counts follow current filter (WYSIWYG)</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Every filter narrows the visible set. Pill counts = list count for the same tab. SLA-breached chip also narrows.</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>Regression for 3f0df68 pill-count parity (was fixed on tickets, exec queue may share the pattern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="60" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>EX-03</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Exec Queue — Actions</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Escalate action creates activity + notifies stakeholders</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>1. Open an SLA-breached ticket
+2. Click Escalate; add reason
+3. Check activity log + notification dispatch</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Activity row: action_type='escalated', actor=admin, reason preserved. Notification fires (log line visible).</t>
+        </is>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr"/>
+    </row>
+    <row r="155" ht="60" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>EX-04</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>Exec Queue — Actions</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>SLA-breached chip filter — WYSIWYG count</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>1. Note the breached chip count
+2. Apply a filter that narrows the queue
+3. Verify chip count updates to match the filtered view</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Breached chip counts current filter set (0cde4ed reversal — chip is filter-aware, not office-wide).</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr"/>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Regression for 0cde4ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="60" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>DP-01</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Dept — Access</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>dept_officer login → sees only own dept's tickets</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as a dept_officer (dept_a)
+2. Try to open a ticket from dept_b directly via URL</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>dept_a's tickets visible. dept_b's ticket → 403 with clean 'not authorized' message (not 500).</t>
+        </is>
+      </c>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr"/>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Regression for f40c2f6 HTTPException import fix (clean 403 not 500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="60" customHeight="1">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>DP-02</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>Dept — Lifecycle</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Accept flow — status → IN_PROGRESS, accepted_at + accepted_by set</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a ticket routed to caller's dept in ASSIGNED state
+2. Click Accept
+3. Verify state + activity log</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Ticket.status = IN_PROGRESS. accepted_at / accepted_by populated. Activity row action_type='department_accepted'.</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr"/>
+      <c r="I157" s="5" t="inlineStr"/>
+    </row>
+    <row r="158" ht="60" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>DP-03</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Dept — Lifecycle</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Progress update — note + optional pct</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>1. On an IN_PROGRESS ticket, post a progress update with a note + 40% pct
+2. Verify activity log + ticket state</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Activity row: action_type='progress_update', note preserved, payload.progress_pct=40. Ticket.progress_pct=40.</t>
+        </is>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr"/>
+      <c r="I158" s="5" t="inlineStr"/>
+    </row>
+    <row r="159" ht="60" customHeight="1">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>DP-04</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>Dept — Lifecycle</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Forward to another dept — reason required, cannot self-forward</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>1. On an owned ticket, click Forward → target = own dept → expect reject
+2. Forward without reason → expect reject
+3. Forward to dept_b with reason 'requires their expertise'</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Self-forward returns 400 'Cannot forward to the same department'. No reason returns 400 'A reason is required'. Valid forward: status=ASSIGNED, department=dept_b, accepted_at cleared, activity 'department_forwarded' with reason in payload.</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr"/>
+    </row>
+    <row r="160" ht="60" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>DP-05</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Dept — Lifecycle</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Resolve — mandatory remarks + at least one proof attachment</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>1. On IN_PROGRESS, click Resolve without remarks → reject
+2. Add remarks, no attachment → reject
+3. Add remarks + one proof file → succeed</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Both empty cases return 400 with clean message. Valid resolve: status=RESOLVED, remarks stored, attachment linked, activity 'resolved'.</t>
+        </is>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr"/>
+      <c r="I160" s="5" t="inlineStr"/>
+    </row>
+    <row r="161" ht="60" customHeight="1">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>DP-06</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Dept — Attachments</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>All three attachment namespaces resolve correctly for dept</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a ticket derived from an AI upload → click the citizen's original PDF (ai_uploads/…)
+2. Open an appointment attachment (attachments/…)
+3. Open a ticket attachment uploaded by PA (ticket_attachments/…)
+4. Try a proposals/ URL — expect 403</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>First three render inline (200). proposals/ → 403 (no UI for it). Dept activity trail includes upload if they added one — regression for 7fd0118.</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr"/>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>Combines cbc9c8c (ai_uploads/ branch) + 7fd0118 (dept-add-attachment threads ticket_id + actor) + fail-closed defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="60" customHeight="1">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>DP-07</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Dept — Lifecycle</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Reopen from PA side → ticket comes back to dept</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>1. Dept resolves a ticket
+2. PA reopens it via ticket drawer
+3. Verify state on dept portal</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>Ticket.status=REOPENED, visible again in dept's active list. Activity log has both 'resolved' and 'reopened' rows.</t>
+        </is>
+      </c>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr"/>
+      <c r="I162" s="5" t="inlineStr"/>
+    </row>
+    <row r="163" ht="60" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>MN-01</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Minister — Access</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Minister login → PWA loads with service worker</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in via /minister/login
+2. Verify /minister/sw.js registers cleanly
+3. Check service worker scope</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Login sets minister_session. /minister/sw.js served with Content-Type application/javascript + Service-Worker-Allowed: /minister/ (next.config.mjs headers). PWA installable.</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr"/>
+      <c r="I163" s="5" t="inlineStr"/>
+    </row>
+    <row r="164" ht="60" customHeight="1">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>MN-02</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Minister — Read-only</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>No mutation controls visible — read-only surface</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a ticket / association / proposal on the minister PWA
+2. Scan for edit / assign / approve / reject buttons</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Zero mutation controls. Only view + navigation. Attempting a mutation API call via devtools → 403.</t>
+        </is>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr"/>
+      <c r="I164" s="5" t="inlineStr"/>
+    </row>
+    <row r="165" ht="60" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>MN-03</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Minister — File access</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>/api/files → /minister/api/files URL rewrite works</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a ticket with an attachment
+2. Inspect the attachment URL in devtools</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>URLs in the payload rewritten from /api/files/… to /minister/api/files/… (minister.py:208). Fetch succeeds via minister_session cookie.</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr"/>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>Regression for the deep-rewrite pattern in minister.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="60" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>MN-04</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Minister — File access</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>Attachment preview iframe renders (CI-89 regression from minister surface)</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a ticket / association with a PDF attachment on the minister PWA
+2. Verify the iframe renders</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>PDF renders inline (not 'blocked:other'). /minister/api/files/… is in the middleware's embeddable-prefix list (see main.py _EMBEDDABLE_PREFIXES).</t>
+        </is>
+      </c>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr"/>
+      <c r="I166" s="5" t="inlineStr"/>
+    </row>
+    <row r="167" ht="60" customHeight="1">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>MN-05</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Minister — Scoping</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Ministry-scoped view — sees only assigned-ministry rows</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in as a minister assigned to ministry X
+2. Load list — verify all rows are ministry-X
+3. Try to open a ticket from ministry Y directly</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>List filtered to ministry X only. Direct-URL to another ministry's ticket → 403 / redirect, not silent view.</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr"/>
+      <c r="I167" s="5" t="inlineStr"/>
+    </row>
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>T5-01</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>RBAC gates on all escalation endpoints (Group 3 audit)</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>1. For each of the 6 escalation endpoints (accept / forward / progress / resolve / reopen / escalate), try calling as an unauthorized role
+2. Expect 403 on every one</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>Every endpoint gates by role. dept_officer can't hit exec-only routes. minister can't mutate. Cross-dept dept_officer gets 403 on other-dept tickets.</t>
+        </is>
+      </c>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr"/>
+      <c r="I168" s="5" t="inlineStr">
+        <is>
+          <t>Regression for Group 3 RBAC hardening (audit fix batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>T5-02</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>i18n copy — no 'referral' vocabulary drift in exec/dept surfaces</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>1. Scan the Executive Queue + Dept portal UI
+2. Look for stray 'referral' / 'refer' terms</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>Zero 'referral' vocabulary — replaced with 'petition' / 'case' / 'ticket' terminology per 2599564. Consistent with citizen-facing form.</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr"/>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>Regression for 2599564 i18n(exec-queue) cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>T5-03</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>Polished error toasts across all three surfaces</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>1. Trigger failures on Exec Queue, Dept portal, Minister PWA
+2. Screenshot each toast</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>Every message user-friendly. Zero tracebacks / raw HTTP codes / 'gemini-*'. Routed through businessMessage() (errors.ts).</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr"/>
+      <c r="I170" s="5" t="inlineStr"/>
+    </row>
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>T5-04</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Mobile viewport (375px) — Minister PWA usable</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>1. Resize to 375x812
+2. Log in as minister → open a ticket
+3. Verify layout + interaction</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>PWA scales to mobile. Nav + drawers usable with thumbs. No horizontal body scroll. Service worker still registered.</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr"/>
+      <c r="I171" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I151"/>
+  <autoFilter ref="A1:I171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -666,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8195,215 +8195,260 @@
     <row r="167" ht="60" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
         <is>
+          <t>MN-04b</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Minister — File access</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Event photos + audio render on minister PWA (events/ namespace)</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>1. Open /minister/events
+2. Click an event with a photo → verify image renders
+3. Play an event's voice audio → verify it streams</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>Both render (200). Prior bug: 403 because minister._authorize had no `events/` branch and fell through to fail-closed deny. Sentinel keys like `events/manual` still 403 (no actual bytes).</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr"/>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>USER-REPORTED. Fixed by adding events/ branch to minister._authorize gated on InvitationEvent.image_path OR audio_path == key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="60" customHeight="1">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
           <t>MN-05</t>
         </is>
       </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="B168" s="5" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="C168" s="5" t="inlineStr">
         <is>
           <t>Minister — Scoping</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>Ministry-scoped view — sees only assigned-ministry rows</t>
         </is>
       </c>
-      <c r="E167" s="5" t="inlineStr">
+      <c r="E168" s="5" t="inlineStr">
         <is>
           <t>1. Log in as a minister assigned to ministry X
 2. Load list — verify all rows are ministry-X
 3. Try to open a ticket from ministry Y directly</t>
         </is>
       </c>
-      <c r="F167" s="5" t="inlineStr">
+      <c r="F168" s="5" t="inlineStr">
         <is>
           <t>List filtered to ministry X only. Direct-URL to another ministry's ticket → 403 / redirect, not silent view.</t>
         </is>
       </c>
-      <c r="G167" s="8" t="inlineStr">
+      <c r="G168" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H167" s="5" t="inlineStr"/>
-      <c r="I167" s="5" t="inlineStr"/>
-    </row>
-    <row r="168" ht="60" customHeight="1">
-      <c r="A168" s="5" t="inlineStr">
+      <c r="H168" s="5" t="inlineStr"/>
+      <c r="I168" s="5" t="inlineStr"/>
+    </row>
+    <row r="169" ht="60" customHeight="1">
+      <c r="A169" s="5" t="inlineStr">
         <is>
           <t>T5-01</t>
         </is>
       </c>
-      <c r="B168" s="5" t="inlineStr">
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr">
         <is>
           <t>Cross-cutting</t>
         </is>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D169" s="5" t="inlineStr">
         <is>
           <t>RBAC gates on all escalation endpoints (Group 3 audit)</t>
         </is>
       </c>
-      <c r="E168" s="5" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>1. For each of the 6 escalation endpoints (accept / forward / progress / resolve / reopen / escalate), try calling as an unauthorized role
 2. Expect 403 on every one</t>
         </is>
       </c>
-      <c r="F168" s="5" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
         <is>
           <t>Every endpoint gates by role. dept_officer can't hit exec-only routes. minister can't mutate. Cross-dept dept_officer gets 403 on other-dept tickets.</t>
         </is>
       </c>
-      <c r="G168" s="8" t="inlineStr">
+      <c r="G169" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H168" s="5" t="inlineStr"/>
-      <c r="I168" s="5" t="inlineStr">
+      <c r="H169" s="5" t="inlineStr"/>
+      <c r="I169" s="5" t="inlineStr">
         <is>
           <t>Regression for Group 3 RBAC hardening (audit fix batch)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="60" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
+    <row r="170" ht="60" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>T5-02</t>
         </is>
       </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="B170" s="5" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="C169" s="5" t="inlineStr">
+      <c r="C170" s="5" t="inlineStr">
         <is>
           <t>Cross-cutting</t>
         </is>
       </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>i18n copy — no 'referral' vocabulary drift in exec/dept surfaces</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
+      <c r="E170" s="5" t="inlineStr">
         <is>
           <t>1. Scan the Executive Queue + Dept portal UI
 2. Look for stray 'referral' / 'refer' terms</t>
         </is>
       </c>
-      <c r="F169" s="5" t="inlineStr">
+      <c r="F170" s="5" t="inlineStr">
         <is>
           <t>Zero 'referral' vocabulary — replaced with 'petition' / 'case' / 'ticket' terminology per 2599564. Consistent with citizen-facing form.</t>
         </is>
       </c>
-      <c r="G169" s="8" t="inlineStr">
+      <c r="G170" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H169" s="5" t="inlineStr"/>
-      <c r="I169" s="5" t="inlineStr">
+      <c r="H170" s="5" t="inlineStr"/>
+      <c r="I170" s="5" t="inlineStr">
         <is>
           <t>Regression for 2599564 i18n(exec-queue) cleanup</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="60" customHeight="1">
-      <c r="A170" s="5" t="inlineStr">
+    <row r="171" ht="60" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>T5-03</t>
         </is>
       </c>
-      <c r="B170" s="5" t="inlineStr">
+      <c r="B171" s="5" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="C170" s="5" t="inlineStr">
+      <c r="C171" s="5" t="inlineStr">
         <is>
           <t>Cross-cutting</t>
         </is>
       </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>Polished error toasts across all three surfaces</t>
         </is>
       </c>
-      <c r="E170" s="5" t="inlineStr">
+      <c r="E171" s="5" t="inlineStr">
         <is>
           <t>1. Trigger failures on Exec Queue, Dept portal, Minister PWA
 2. Screenshot each toast</t>
         </is>
       </c>
-      <c r="F170" s="5" t="inlineStr">
+      <c r="F171" s="5" t="inlineStr">
         <is>
           <t>Every message user-friendly. Zero tracebacks / raw HTTP codes / 'gemini-*'. Routed through businessMessage() (errors.ts).</t>
         </is>
       </c>
-      <c r="G170" s="8" t="inlineStr">
+      <c r="G171" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H170" s="5" t="inlineStr"/>
-      <c r="I170" s="5" t="inlineStr"/>
-    </row>
-    <row r="171" ht="60" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="H171" s="5" t="inlineStr"/>
+      <c r="I171" s="5" t="inlineStr"/>
+    </row>
+    <row r="172" ht="60" customHeight="1">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>T5-04</t>
         </is>
       </c>
-      <c r="B171" s="5" t="inlineStr">
+      <c r="B172" s="5" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="C171" s="5" t="inlineStr">
+      <c r="C172" s="5" t="inlineStr">
         <is>
           <t>Cross-cutting</t>
         </is>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>Mobile viewport (375px) — Minister PWA usable</t>
         </is>
       </c>
-      <c r="E171" s="5" t="inlineStr">
+      <c r="E172" s="5" t="inlineStr">
         <is>
           <t>1. Resize to 375x812
 2. Log in as minister → open a ticket
 3. Verify layout + interaction</t>
         </is>
       </c>
-      <c r="F171" s="5" t="inlineStr">
+      <c r="F172" s="5" t="inlineStr">
         <is>
           <t>PWA scales to mobile. Nav + drawers usable with thumbs. No horizontal body scroll. Service worker still registered.</t>
         </is>
       </c>
-      <c r="G171" s="8" t="inlineStr">
+      <c r="G172" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H171" s="5" t="inlineStr"/>
-      <c r="I171" s="5" t="inlineStr"/>
+      <c r="H172" s="5" t="inlineStr"/>
+      <c r="I172" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I171"/>
+  <autoFilter ref="A1:I172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/qa/test-cases.xlsx
+++ b/qa/test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P5 — Executive / Dept / Minister</t>
+          <t>P6 — Cross-cutting sanity</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>148</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>150</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +666,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>91%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7594,12 +7594,16 @@
           <t>pa_admin loads. dept_officer redirected to /tickets. No cross-role leak.</t>
         </is>
       </c>
-      <c r="G152" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr"/>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I152" s="5" t="inlineStr"/>
     </row>
     <row r="153" ht="60" customHeight="1">
@@ -7635,12 +7639,16 @@
           <t>Every filter narrows the visible set. Pill counts = list count for the same tab. SLA-breached chip also narrows.</t>
         </is>
       </c>
-      <c r="G153" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
           <t>Regression for 3f0df68 pill-count parity (was fixed on tickets, exec queue may share the pattern)</t>
@@ -7680,12 +7688,16 @@
           <t>Activity row: action_type='escalated', actor=admin, reason preserved. Notification fires (log line visible).</t>
         </is>
       </c>
-      <c r="G154" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H154" s="5" t="inlineStr"/>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I154" s="5" t="inlineStr"/>
     </row>
     <row r="155" ht="60" customHeight="1">
@@ -7721,12 +7733,16 @@
           <t>Breached chip counts current filter set (0cde4ed reversal — chip is filter-aware, not office-wide).</t>
         </is>
       </c>
-      <c r="G155" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="inlineStr"/>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
           <t>Regression for 0cde4ed</t>
@@ -7765,12 +7781,16 @@
           <t>dept_a's tickets visible. dept_b's ticket → 403 with clean 'not authorized' message (not 500).</t>
         </is>
       </c>
-      <c r="G156" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H156" s="5" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
           <t>Regression for f40c2f6 HTTPException import fix (clean 403 not 500)</t>
@@ -7810,12 +7830,16 @@
           <t>Ticket.status = IN_PROGRESS. accepted_at / accepted_by populated. Activity row action_type='department_accepted'.</t>
         </is>
       </c>
-      <c r="G157" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr"/>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I157" s="5" t="inlineStr"/>
     </row>
     <row r="158" ht="60" customHeight="1">
@@ -7850,12 +7874,16 @@
           <t>Activity row: action_type='progress_update', note preserved, payload.progress_pct=40. Ticket.progress_pct=40.</t>
         </is>
       </c>
-      <c r="G158" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H158" s="5" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I158" s="5" t="inlineStr"/>
     </row>
     <row r="159" ht="60" customHeight="1">
@@ -7891,12 +7919,16 @@
           <t>Self-forward returns 400 'Cannot forward to the same department'. No reason returns 400 'A reason is required'. Valid forward: status=ASSIGNED, department=dept_b, accepted_at cleared, activity 'department_forwarded' with reason in payload.</t>
         </is>
       </c>
-      <c r="G159" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr"/>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I159" s="5" t="inlineStr"/>
     </row>
     <row r="160" ht="60" customHeight="1">
@@ -7932,12 +7964,16 @@
           <t>Both empty cases return 400 with clean message. Valid resolve: status=RESOLVED, remarks stored, attachment linked, activity 'resolved'.</t>
         </is>
       </c>
-      <c r="G160" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H160" s="5" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I160" s="5" t="inlineStr"/>
     </row>
     <row r="161" ht="60" customHeight="1">
@@ -7974,12 +8010,16 @@
           <t>First three render inline (200). proposals/ → 403 (no UI for it). Dept activity trail includes upload if they added one — regression for 7fd0118.</t>
         </is>
       </c>
-      <c r="G161" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
           <t>Combines cbc9c8c (ai_uploads/ branch) + 7fd0118 (dept-add-attachment threads ticket_id + actor) + fail-closed defaults</t>
@@ -8019,12 +8059,16 @@
           <t>Ticket.status=REOPENED, visible again in dept's active list. Activity log has both 'resolved' and 'reopened' rows.</t>
         </is>
       </c>
-      <c r="G162" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H162" s="5" t="inlineStr"/>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I162" s="5" t="inlineStr"/>
     </row>
     <row r="163" ht="60" customHeight="1">
@@ -8060,12 +8104,16 @@
           <t>Login sets minister_session. /minister/sw.js served with Content-Type application/javascript + Service-Worker-Allowed: /minister/ (next.config.mjs headers). PWA installable.</t>
         </is>
       </c>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H163" s="5" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I163" s="5" t="inlineStr"/>
     </row>
     <row r="164" ht="60" customHeight="1">
@@ -8100,12 +8148,16 @@
           <t>Zero mutation controls. Only view + navigation. Attempting a mutation API call via devtools → 403.</t>
         </is>
       </c>
-      <c r="G164" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H164" s="5" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I164" s="5" t="inlineStr"/>
     </row>
     <row r="165" ht="60" customHeight="1">
@@ -8140,12 +8192,16 @@
           <t>URLs in the payload rewritten from /api/files/… to /minister/api/files/… (minister.py:208). Fetch succeeds via minister_session cookie.</t>
         </is>
       </c>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
           <t>Regression for the deep-rewrite pattern in minister.py</t>
@@ -8184,12 +8240,16 @@
           <t>PDF renders inline (not 'blocked:other'). /minister/api/files/… is in the middleware's embeddable-prefix list (see main.py _EMBEDDABLE_PREFIXES).</t>
         </is>
       </c>
-      <c r="G166" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H166" s="5" t="inlineStr"/>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I166" s="5" t="inlineStr"/>
     </row>
     <row r="167" ht="60" customHeight="1">
@@ -8225,12 +8285,16 @@
           <t>Both render (200). Prior bug: 403 because minister._authorize had no `events/` branch and fell through to fail-closed deny. Sentinel keys like `events/manual` still 403 (no actual bytes).</t>
         </is>
       </c>
-      <c r="G167" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
           <t>USER-REPORTED. Fixed by adding events/ branch to minister._authorize gated on InvitationEvent.image_path OR audio_path == key.</t>
@@ -8270,12 +8334,16 @@
           <t>List filtered to ministry X only. Direct-URL to another ministry's ticket → 403 / redirect, not silent view.</t>
         </is>
       </c>
-      <c r="G168" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I168" s="5" t="inlineStr"/>
     </row>
     <row r="169" ht="60" customHeight="1">
@@ -8310,12 +8378,16 @@
           <t>Every endpoint gates by role. dept_officer can't hit exec-only routes. minister can't mutate. Cross-dept dept_officer gets 403 on other-dept tickets.</t>
         </is>
       </c>
-      <c r="G169" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr"/>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
           <t>Regression for Group 3 RBAC hardening (audit fix batch)</t>
@@ -8354,12 +8426,16 @@
           <t>Zero 'referral' vocabulary — replaced with 'petition' / 'case' / 'ticket' terminology per 2599564. Consistent with citizen-facing form.</t>
         </is>
       </c>
-      <c r="G170" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H170" s="5" t="inlineStr"/>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
           <t>Regression for 2599564 i18n(exec-queue) cleanup</t>
@@ -8398,12 +8474,16 @@
           <t>Every message user-friendly. Zero tracebacks / raw HTTP codes / 'gemini-*'. Routed through businessMessage() (errors.ts).</t>
         </is>
       </c>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
       <c r="I171" s="5" t="inlineStr"/>
     </row>
     <row r="172" ht="60" customHeight="1">
@@ -8439,16 +8519,674 @@
           <t>PWA scales to mobile. Nav + drawers usable with thumbs. No horizontal body scroll. Service worker still registered.</t>
         </is>
       </c>
-      <c r="G172" s="8" t="inlineStr">
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>Verified on Railway</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr"/>
+    </row>
+    <row r="173" ht="60" customHeight="1">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>P6-01</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>Auth boundaries</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>Cross-role RBAC sweep on the 6 escalation endpoints</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>1. Enumerate: accept / forward / progress / resolve / reopen / escalate
+2. For each, call as pa_admin, dept_officer (own dept), dept_officer (other dept), minister, unauth
+3. Verify allow/deny matrix</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>pa_admin: accept ❌ (dept only) / forward ❌ / progress ❌ / resolve ❌ / reopen ✅ / escalate ✅. dept_officer own: all ✅. dept_officer other: all 403. minister: all 403. unauth: 401 / login redirect.</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H172" s="5" t="inlineStr"/>
-      <c r="I172" s="5" t="inlineStr"/>
+      <c r="H173" s="5" t="inlineStr"/>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>Regression for Group 3 RBAC hardening + f40c2f6 clean 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="60" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>P6-02</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>Auth boundaries</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>Session cookies — HttpOnly + Secure + SameSite</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>1. Log in on each surface (PA / dept / minister / events / crowd)
+2. Inspect Set-Cookie headers in devtools</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>Every session cookie has HttpOnly, Secure (in prod), and SameSite=Lax or Strict. No cookie readable from JS.</t>
+        </is>
+      </c>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr"/>
+      <c r="I174" s="5" t="inlineStr"/>
+    </row>
+    <row r="175" ht="60" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>P6-03</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>Rate limit</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>RATE_LIMIT_ENABLED master switch respected</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>1. Confirm current env has RATE_LIMIT_ENABLED=false — burst 20 requests, verify no 429
+2. If desired, flip to true in a separate env — verify @limiter.limit endpoints return 429 on burst</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>OFF: no rate limiter fires anywhere. ON: individual @limiter.limit endpoints return 429 at their configured rates (3-5/min per IP).</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr"/>
+      <c r="I175" s="5" t="inlineStr">
+        <is>
+          <t>Skipped-in-P1 CI-23 setup validated at the system level</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="60" customHeight="1">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>P6-04</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Perf</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>GZip compression on JSON responses (&gt;1KB)</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>1. curl -H 'Accept-Encoding: gzip' &lt;api endpoint returning &gt;1KB JSON&gt;
+2. Verify Content-Encoding: gzip in response headers</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>Responses &gt;1KB are gzipped. Small (&lt;1KB) responses not gzipped. GZipMiddleware minimum_size=1024 respected.</t>
+        </is>
+      </c>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr"/>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Regression for PERF-17 GZipMiddleware</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="60" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>P6-05</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>Perf</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>/api/venues cache — short public + revalidate</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>1. curl /dashboard/api/venues → inspect Cache-Control header
+2. Repeat within cache window → verify 304 or served from cache</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>Cache-Control: public, max-age=&lt;short&gt;, must-revalidate (or similar). Not immutable, not no-store. Frontend fetch config no longer sends no-cache.</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr"/>
+      <c r="I177" s="5" t="inlineStr">
+        <is>
+          <t>Regression for PERF-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="60" customHeight="1">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>P6-06</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>Perf</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>Immutable file cache invalidates on same-key overwrite</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>1. Upload a PDF, note ETag on GET /dashboard/api/files/&lt;key&gt;
+2. Overwrite the same key with different bytes (via internal MinIO or admin flow)
+3. GET again — verify ETag changed → browser refetches</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>ETag = md5(file_path + size + last_modified + media_type). A same-size overwrite still invalidates because last_modified changed. Cached copies never serve stale bytes.</t>
+        </is>
+      </c>
+      <c r="G178" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr"/>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>Regression for the ETag rebuild fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="60" customHeight="1">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>P6-07</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>IST/UTC drift-free — daily loops + counts + tokens agree on 'today'</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>1. At 23:55 IST (18:25 UTC), submit a petition
+2. Check /counts today bucket + referral daily token + convert-to-petition daily guard
+3. Wait until 00:05 IST next day, repeat</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>All three surfaces treat 'today' as the IST calendar day, not UTC. No off-by-one at day boundaries.</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr"/>
+      <c r="I179" s="5" t="inlineStr">
+        <is>
+          <t>Regression for CORR-07/08/09 IST/UTC drift</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="60" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>P6-08</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>Background task survival — spawn_bg tasks complete</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>1. Trigger a summarisation via appointment submit
+2. Immediately check _BG_TASKS module-level set is retained until task completes
+3. Verify GrievanceSummaryRecord row lands even under concurrent load</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>spawn_bg tasks aren't GC'd mid-flight. Every submitted appointment eventually has a GSR row (unless SDK error).</t>
+        </is>
+      </c>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr"/>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>Regression for CORR-01/02 spawn_bg GC hardening</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="60" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>P6-09</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Security headers</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>Non-file responses stay strict: DENY + frame-ancestors 'none'</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>1. curl /dashboard/api/tickets → inspect headers
+2. Repeat for /api/v1/appointments, /minister/api/tickets, jinja pages</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>Every non-file response has X-Frame-Options: DENY, CSP frame-ancestors 'none', X-Content-Type-Options: nosniff, Referrer-Policy: strict-origin-when-cross-origin, Permissions-Policy present.</t>
+        </is>
+      </c>
+      <c r="G181" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr"/>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>Regression for _SecurityHeadersMiddleware baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="60" customHeight="1">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>P6-10</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Security headers</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>File-serve responses: SAMEORIGIN + frame-ancestors 'self' &lt;CORS&gt;</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>1. curl /dashboard/api/files/&lt;key&gt; → inspect headers
+2. Same for /events/api/files, /minister/api/files, /department/api/files</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>All four prefixes return X-Frame-Options: SAMEORIGIN and CSP frame-ancestors containing 'self' + CORS_ORIGINS entries. Cross-checks the CI-89 iframe fix from every embeddable-asset entry point.</t>
+        </is>
+      </c>
+      <c r="G182" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr"/>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>Regression for 38a64bc scoped iframe relaxation</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="60" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>P6-11</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>AI reliability</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Vertex → direct-API fallback + polished error on both-fail</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>1. Confirm boot log shows 'Vertex AI backend ready (creds=env-content)' — Vertex is primary
+2. Force-fail Vertex temporarily → verify direct-API takes over
+3. Force both to fail → verify polished user-facing error (no traceback)</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>Log line at boot confirms creds source. Vertex outage triggers direct-API fallback silently. Both-fail returns 502 with human message; no raw 'gemini-*' or SDK exception in UI.</t>
+        </is>
+      </c>
+      <c r="G183" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr"/>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>System-wide re-verify of the Vertex overload (commit 6fda89b) + fail-through path</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="60" customHeight="1">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>P6-12</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>File caps</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>MAX_FILE_SIZE_MB + MAX_ATTACHMENTS enforced at every upload path</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>1. Try uploading a 6MB file via: citizen QR upload, PA drawer, dept drawer, event photo
+2. Try uploading an 11th file on an appointment with 10 existing attachments</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>Every path returns clean 4xx with human message. 5MB cap + 10-file per submission cap honoured across surfaces.</t>
+        </is>
+      </c>
+      <c r="G184" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr"/>
+      <c r="I184" s="5" t="inlineStr"/>
+    </row>
+    <row r="185" ht="60" customHeight="1">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>P6-13</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>Filename hygiene</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>Filename sanitization consistent across upload paths</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>1. Try uploading '&lt;script&gt;alert(1)&lt;/script&gt;.pdf', '../../etc/passwd.pdf', a 500-char name via each entry point
+2. Verify storage key + display + PDF preview title all safe</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>All entry points route through _sanitize_filename. Path traversal never escapes uploads/. XSS in filename escaped everywhere it's rendered. No 500 on very long names.</t>
+        </is>
+      </c>
+      <c r="G185" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr"/>
+      <c r="I185" s="5" t="inlineStr">
+        <is>
+          <t>CITZ-02 regression, cross-surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="60" customHeight="1">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>P6-14</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>PII at rest</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>Citizen mobile encrypted + blind-indexed + masked on read</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit an appointment with a specific mobile (e.g. 9876543210)
+2. Query the DB — verify encrypted_mobile is Fernet-encrypted (not plaintext), mobile_blind_index is a hex hash
+3. Open the appointment in every UI surface — verify mobile shown as ******3210</t>
+        </is>
+      </c>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>Plaintext mobile never in DB. Blind index enables dedup lookups. Every read surface masks the mobile — PA drawer, dept drawer, minister PWA, activity log, list rows.</t>
+        </is>
+      </c>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr"/>
+      <c r="I186" s="5" t="inlineStr"/>
+    </row>
+    <row r="187" ht="60" customHeight="1">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>P6-15</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>Prod safety</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>assert_production_ready refuses on unsafe defaults</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>1. Simulate each unsafe config in isolation: placeholder SECRET_KEY, default staff creds, localhost in CORS_ORIGINS, short SECRET_KEY, COOKIE_SECURE=false in prod
+2. Verify startup refuses with clear message</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Each unsafe default triggers a startup abort with a message pointing at the exact config. TestProdReadyGates in tests/test_pre_prod_fixes.py covers this at unit level; verify runtime behaviour matches.</t>
+        </is>
+      </c>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr"/>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>Regression for Group 2 prod-safety hardening + the config.py DEBUG-remote-DB guard (currently disabled per user's intentional edit at config.py:293)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I172"/>
+  <autoFilter ref="A1:I187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>